--- a/.gemini/Sample_Data/OpenSearch及Dynamodb欄位_20251106.xlsx
+++ b/.gemini/Sample_Data/OpenSearch及Dynamodb欄位_20251106.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YCLIN\Desktop\WorkSpace\測試專案\NO3._dbSDK_Imporve\.gemini\Sample_Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\YCLIN\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970670F3-A7B9-4C57-8B0F-D37BA6183AEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D57D952-0C0D-4765-96E7-F5F73335523A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="887" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="902" uniqueCount="354">
   <si>
     <t>資料庫</t>
   </si>
@@ -429,9 +429,6 @@
     <t>賣場編號</t>
   </si>
   <si>
-    <t>cgdd_cgdmid</t>
-  </si>
-  <si>
     <t>TopHit</t>
   </si>
   <si>
@@ -452,16 +449,10 @@
     <t>商品編號</t>
   </si>
   <si>
-    <t>cgdd_id</t>
-  </si>
-  <si>
     <t>Cood_CgdsId</t>
   </si>
   <si>
     <t>商品規格編號</t>
-  </si>
-  <si>
-    <t>cood_cgdsid</t>
   </si>
   <si>
     <t>Group By</t>
@@ -1089,152 +1080,30 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>coodItems.cgddCgdmid</t>
-  </si>
-  <si>
-    <t>coodItems.cgddId</t>
-  </si>
-  <si>
-    <t>coodItems.coodImagePath</t>
-  </si>
-  <si>
-    <t>coodItems.coodName</t>
-  </si>
-  <si>
-    <t>coodItems.coodQty</t>
-  </si>
-  <si>
-    <t>coodItems.coodCgdsId</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>cooc_deliver_method</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>coocDeliverMethod</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>esmm_ship_no</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>esmmShipNo</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>esmm_leavestoredate_b</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>esmmLeavestoredateB</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>esmm_rcv_totalamt</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>smmRcvTotalAmt</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>coomstatus</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>coomname</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>coomTempType</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>coomCreateDatetime</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>coomCuamCid</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>coomRcvTotalAmt</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>esmlStatusShippingDatetime</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>esms_dlvstatus_seller_pickup</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>esmsDlvstatusSellerPickup</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>esmsScStatusReturning</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>sellerQaNeverReplyCount</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>buyerQaNeverReplyCount</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
     <t>cood_items</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>CoodItems</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>coocNo</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>coocPaymentType</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>coocPaymentPayDatetime</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>coocOrdChannelKind</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>coocMemSid</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>coodNames</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>esmlStatusFinishDatetime</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsReturnShipping</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>CrsaApplied</t>
-    <phoneticPr fontId="14" type="noConversion"/>
-  </si>
-  <si>
-    <t>coomNo</t>
-  </si>
-  <si>
     <t>Text</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
@@ -1290,10 +1159,143 @@
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>coomCuamCid</t>
-  </si>
-  <si>
     <t>Unique Index</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>coom_rcv_totalamt</t>
+  </si>
+  <si>
+    <t>esmm_rcv_totalamt</t>
+  </si>
+  <si>
+    <t>esmm_leavestoredate_b</t>
+  </si>
+  <si>
+    <t>esms_dlvstatus_seller_pickup</t>
+  </si>
+  <si>
+    <t>crsa_applied</t>
+  </si>
+  <si>
+    <t>cgdd_cgdmid</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>coodItems.cgdd_cgdmid</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>cgdd_id</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>coodItems.cgdd_id</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>cood_cgdsid</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>coodItems.cood_cgdsid</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>coodItems.cood_name</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>cood_qty</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>coodItems.cood_qty</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>cood_image_path</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>coodItems.cood_image_path</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>ElasticSearch</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF000000"/>
+        <rFont val="微軟正黑體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>索引設計</t>
+    </r>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>idx_id</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>idx_index</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>"order"+{coom_no</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>的第四個字元取3位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+      </rPr>
+      <t>；</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Microsoft JhengHei"/>
+        <family val="2"/>
+      </rPr>
+      <t>範例</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>order604(CM2604XXXX)</t>
+    </r>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -1301,7 +1303,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1453,6 +1455,33 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Microsoft JhengHei"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="細明體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -1510,7 +1539,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="101">
+  <borders count="102">
     <border>
       <left/>
       <right/>
@@ -2726,11 +2755,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="271">
+  <cellXfs count="273">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3130,9 +3174,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3142,9 +3183,6 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3286,9 +3324,6 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3349,9 +3384,6 @@
     <xf numFmtId="0" fontId="1" fillId="5" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3373,6 +3405,21 @@
     <xf numFmtId="0" fontId="19" fillId="9" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="101" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="100" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3382,155 +3429,158 @@
     <xf numFmtId="0" fontId="20" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="87" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="70" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="92" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="88" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="92" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="78" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="85" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -3767,11 +3817,11 @@
     <col min="3" max="3" width="17" customWidth="1"/>
     <col min="4" max="4" width="8.5" customWidth="1"/>
     <col min="5" max="5" width="19.375" customWidth="1"/>
-    <col min="6" max="6" width="6.625" customWidth="1"/>
+    <col min="6" max="6" width="22.625" customWidth="1"/>
     <col min="7" max="7" width="17.625" customWidth="1"/>
     <col min="8" max="8" width="25.625" customWidth="1"/>
-    <col min="9" max="9" width="33.5" customWidth="1"/>
-    <col min="10" max="10" width="4.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5" customWidth="1"/>
     <col min="11" max="11" width="15.875" customWidth="1"/>
     <col min="12" max="12" width="34.25" customWidth="1"/>
     <col min="13" max="13" width="24.875" customWidth="1"/>
@@ -3784,28 +3834,28 @@
   <sheetData>
     <row r="1" spans="1:25" ht="17.25" thickBot="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="238" t="s">
+      <c r="B1" s="261" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="240"/>
-      <c r="G1" s="224" t="s">
+      <c r="C1" s="262"/>
+      <c r="D1" s="262"/>
+      <c r="E1" s="262"/>
+      <c r="F1" s="263"/>
+      <c r="G1" s="252" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="225"/>
-      <c r="I1" s="225"/>
+      <c r="H1" s="253"/>
+      <c r="I1" s="253"/>
       <c r="J1" s="2"/>
       <c r="K1" s="3"/>
       <c r="L1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="228" t="s">
-        <v>312</v>
-      </c>
-      <c r="N1" s="229"/>
-      <c r="O1" s="230"/>
+      <c r="M1" s="256" t="s">
+        <v>309</v>
+      </c>
+      <c r="N1" s="257"/>
+      <c r="O1" s="258"/>
       <c r="P1" s="6"/>
       <c r="Q1" s="6"/>
       <c r="R1" s="6"/>
@@ -3817,7 +3867,7 @@
       <c r="X1" s="6"/>
       <c r="Y1" s="6"/>
     </row>
-    <row r="2" spans="1:25" ht="27.75" thickBot="1">
+    <row r="2" spans="1:25" ht="16.5" thickBot="1">
       <c r="A2" s="7" t="s">
         <v>3</v>
       </c>
@@ -3843,7 +3893,7 @@
         <v>10</v>
       </c>
       <c r="I2" s="9" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="J2" s="9"/>
       <c r="K2" s="9" t="s">
@@ -3856,11 +3906,11 @@
       <c r="N2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="O2" s="204" t="s">
-        <v>313</v>
+      <c r="O2" s="201" t="s">
+        <v>310</v>
       </c>
       <c r="P2" s="6" t="s">
-        <v>358</v>
+        <v>323</v>
       </c>
       <c r="Q2" s="6"/>
       <c r="R2" s="6"/>
@@ -3877,7 +3927,7 @@
         <f t="shared" ref="A3:A34" si="0">ROW()-2</f>
         <v>1</v>
       </c>
-      <c r="B3" s="233" t="s">
+      <c r="B3" s="244" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="12" t="s">
@@ -3904,15 +3954,15 @@
         <v>18</v>
       </c>
       <c r="L3" s="21"/>
-      <c r="M3" s="202" t="s">
-        <v>351</v>
+      <c r="M3" s="199" t="s">
+        <v>16</v>
       </c>
       <c r="N3" s="6"/>
-      <c r="O3" s="204" t="s">
-        <v>352</v>
+      <c r="O3" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P3" s="6" t="s">
-        <v>359</v>
+        <v>324</v>
       </c>
       <c r="R3" s="6"/>
       <c r="S3" s="6"/>
@@ -3928,7 +3978,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B4" s="220"/>
+      <c r="B4" s="231"/>
       <c r="C4" s="23" t="s">
         <v>19</v>
       </c>
@@ -3953,12 +4003,12 @@
         <v>23</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="202" t="s">
-        <v>329</v>
+      <c r="M4" s="199" t="s">
+        <v>22</v>
       </c>
       <c r="N4" s="6"/>
-      <c r="O4" s="204" t="s">
-        <v>352</v>
+      <c r="O4" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P4" s="6"/>
       <c r="R4" s="6"/>
@@ -3975,7 +4025,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="220"/>
+      <c r="B5" s="231"/>
       <c r="C5" s="33" t="s">
         <v>24</v>
       </c>
@@ -4002,12 +4052,12 @@
         <v>29</v>
       </c>
       <c r="L5" s="21"/>
-      <c r="M5" s="202" t="s">
-        <v>328</v>
+      <c r="M5" s="199" t="s">
+        <v>28</v>
       </c>
       <c r="N5" s="6"/>
-      <c r="O5" s="204" t="s">
-        <v>352</v>
+      <c r="O5" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P5" s="6"/>
       <c r="R5" s="6"/>
@@ -4024,7 +4074,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="220"/>
+      <c r="B6" s="231"/>
       <c r="C6" s="33" t="s">
         <v>30</v>
       </c>
@@ -4049,12 +4099,12 @@
         <v>29</v>
       </c>
       <c r="L6" s="44"/>
-      <c r="M6" s="202" t="s">
-        <v>330</v>
+      <c r="M6" s="199" t="s">
+        <v>33</v>
       </c>
       <c r="N6" s="6"/>
-      <c r="O6" s="204" t="s">
-        <v>352</v>
+      <c r="O6" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P6" s="6"/>
       <c r="R6" s="6"/>
@@ -4071,7 +4121,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="220"/>
+      <c r="B7" s="231"/>
       <c r="C7" s="45" t="s">
         <v>34</v>
       </c>
@@ -4094,12 +4144,12 @@
         <v>39</v>
       </c>
       <c r="L7" s="44"/>
-      <c r="M7" s="202" t="s">
-        <v>331</v>
+      <c r="M7" s="199" t="s">
+        <v>37</v>
       </c>
       <c r="N7" s="6"/>
-      <c r="O7" s="204" t="s">
-        <v>354</v>
+      <c r="O7" s="201" t="s">
+        <v>319</v>
       </c>
       <c r="P7" s="6"/>
       <c r="R7" s="6"/>
@@ -4116,7 +4166,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="220"/>
+      <c r="B8" s="231"/>
       <c r="C8" s="50" t="s">
         <v>40</v>
       </c>
@@ -4141,12 +4191,12 @@
         <v>29</v>
       </c>
       <c r="L8" s="44"/>
-      <c r="M8" s="202" t="s">
-        <v>332</v>
+      <c r="M8" s="199" t="s">
+        <v>43</v>
       </c>
       <c r="N8" s="6"/>
-      <c r="O8" s="204" t="s">
-        <v>352</v>
+      <c r="O8" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P8" s="6"/>
       <c r="R8" s="6"/>
@@ -4163,7 +4213,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="221"/>
+      <c r="B9" s="232"/>
       <c r="C9" s="54" t="s">
         <v>44</v>
       </c>
@@ -4175,7 +4225,7 @@
       </c>
       <c r="F9" s="57"/>
       <c r="G9" s="58" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="H9" s="59"/>
       <c r="I9" s="60" t="s">
@@ -4188,12 +4238,12 @@
       <c r="L9" s="63" t="s">
         <v>48</v>
       </c>
-      <c r="M9" s="202" t="s">
-        <v>333</v>
+      <c r="M9" s="199" t="s">
+        <v>334</v>
       </c>
       <c r="N9" s="6"/>
-      <c r="O9" s="204" t="s">
-        <v>353</v>
+      <c r="O9" s="201" t="s">
+        <v>318</v>
       </c>
       <c r="P9" s="6"/>
       <c r="R9" s="6"/>
@@ -4210,7 +4260,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="233" t="s">
+      <c r="B10" s="244" t="s">
         <v>49</v>
       </c>
       <c r="C10" s="64" t="s">
@@ -4237,12 +4287,12 @@
         <v>18</v>
       </c>
       <c r="L10" s="70"/>
-      <c r="M10" s="202" t="s">
-        <v>342</v>
+      <c r="M10" s="199" t="s">
+        <v>52</v>
       </c>
       <c r="N10" s="6"/>
-      <c r="O10" s="204" t="s">
-        <v>352</v>
+      <c r="O10" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P10" s="6"/>
       <c r="R10" s="6"/>
@@ -4259,7 +4309,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="220"/>
+      <c r="B11" s="231"/>
       <c r="C11" s="33" t="s">
         <v>53</v>
       </c>
@@ -4284,12 +4334,12 @@
         <v>29</v>
       </c>
       <c r="L11" s="21"/>
-      <c r="M11" s="202" t="s">
-        <v>343</v>
+      <c r="M11" s="199" t="s">
+        <v>55</v>
       </c>
       <c r="N11" s="6"/>
-      <c r="O11" s="204" t="s">
-        <v>352</v>
+      <c r="O11" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P11" s="6"/>
       <c r="R11" s="6"/>
@@ -4306,7 +4356,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="220"/>
+      <c r="B12" s="231"/>
       <c r="C12" s="33" t="s">
         <v>56</v>
       </c>
@@ -4331,12 +4381,12 @@
         <v>39</v>
       </c>
       <c r="L12" s="44"/>
-      <c r="M12" s="202" t="s">
-        <v>344</v>
+      <c r="M12" s="199" t="s">
+        <v>58</v>
       </c>
       <c r="N12" s="6"/>
-      <c r="O12" s="204" t="s">
-        <v>354</v>
+      <c r="O12" s="201" t="s">
+        <v>319</v>
       </c>
       <c r="P12" s="6"/>
       <c r="R12" s="6"/>
@@ -4353,7 +4403,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="220"/>
+      <c r="B13" s="231"/>
       <c r="C13" s="74" t="s">
         <v>59</v>
       </c>
@@ -4365,7 +4415,7 @@
       </c>
       <c r="F13" s="51"/>
       <c r="G13" s="76" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
       <c r="H13" s="77"/>
       <c r="I13" s="30" t="s">
@@ -4378,12 +4428,12 @@
         <v>29</v>
       </c>
       <c r="L13" s="44"/>
-      <c r="M13" s="202" t="s">
-        <v>321</v>
+      <c r="M13" s="199" t="s">
+        <v>61</v>
       </c>
       <c r="N13" s="6"/>
-      <c r="O13" s="204" t="s">
-        <v>352</v>
+      <c r="O13" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P13" s="6"/>
       <c r="R13" s="6"/>
@@ -4400,7 +4450,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="220"/>
+      <c r="B14" s="231"/>
       <c r="C14" s="79" t="s">
         <v>62</v>
       </c>
@@ -4425,12 +4475,12 @@
         <v>29</v>
       </c>
       <c r="L14" s="44"/>
-      <c r="M14" s="202" t="s">
-        <v>345</v>
+      <c r="M14" s="199" t="s">
+        <v>64</v>
       </c>
       <c r="N14" s="6"/>
-      <c r="O14" s="204" t="s">
-        <v>352</v>
+      <c r="O14" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P14" s="6"/>
       <c r="R14" s="6"/>
@@ -4447,7 +4497,7 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="241"/>
+      <c r="B15" s="264"/>
       <c r="C15" s="79" t="s">
         <v>65</v>
       </c>
@@ -4472,12 +4522,12 @@
         <v>29</v>
       </c>
       <c r="L15" s="44"/>
-      <c r="M15" s="202" t="s">
-        <v>346</v>
+      <c r="M15" s="199" t="s">
+        <v>67</v>
       </c>
       <c r="N15" s="6"/>
-      <c r="O15" s="204" t="s">
-        <v>352</v>
+      <c r="O15" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P15" s="6"/>
       <c r="R15" s="6"/>
@@ -4508,7 +4558,7 @@
       </c>
       <c r="F16" s="90"/>
       <c r="G16" s="91" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H16" s="92"/>
       <c r="I16" s="43" t="s">
@@ -4521,12 +4571,12 @@
         <v>23</v>
       </c>
       <c r="L16" s="10"/>
-      <c r="M16" s="202" t="s">
-        <v>347</v>
+      <c r="M16" s="199" t="s">
+        <v>72</v>
       </c>
       <c r="N16" s="6"/>
-      <c r="O16" s="204" t="s">
-        <v>352</v>
+      <c r="O16" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P16" s="6"/>
       <c r="R16" s="6"/>
@@ -4543,7 +4593,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B17" s="242" t="s">
+      <c r="B17" s="265" t="s">
         <v>73</v>
       </c>
       <c r="C17" s="74" t="s">
@@ -4555,11 +4605,11 @@
       <c r="E17" s="75" t="s">
         <v>76</v>
       </c>
-      <c r="F17" s="236" t="s">
+      <c r="F17" s="247" t="s">
         <v>27</v>
       </c>
       <c r="G17" s="93" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="H17" s="94"/>
       <c r="I17" s="68" t="s">
@@ -4572,11 +4622,11 @@
         <v>18</v>
       </c>
       <c r="L17" s="70"/>
-      <c r="M17" s="202" t="s">
-        <v>323</v>
-      </c>
-      <c r="O17" s="204" t="s">
-        <v>352</v>
+      <c r="M17" s="199" t="s">
+        <v>77</v>
+      </c>
+      <c r="O17" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P17" s="6"/>
       <c r="R17" s="6"/>
@@ -4593,7 +4643,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="220"/>
+      <c r="B18" s="231"/>
       <c r="C18" s="33" t="s">
         <v>78</v>
       </c>
@@ -4603,7 +4653,7 @@
       <c r="E18" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="F18" s="243"/>
+      <c r="F18" s="266"/>
       <c r="G18" s="72" t="s">
         <v>80</v>
       </c>
@@ -4618,11 +4668,11 @@
         <v>29</v>
       </c>
       <c r="L18" s="21"/>
-      <c r="M18" s="202" t="s">
-        <v>327</v>
-      </c>
-      <c r="O18" s="204" t="s">
-        <v>352</v>
+      <c r="M18" s="199" t="s">
+        <v>80</v>
+      </c>
+      <c r="O18" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P18" s="6"/>
       <c r="R18" s="6"/>
@@ -4639,7 +4689,7 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="220"/>
+      <c r="B19" s="231"/>
       <c r="C19" s="33" t="s">
         <v>81</v>
       </c>
@@ -4649,9 +4699,9 @@
       <c r="E19" s="40" t="s">
         <v>45</v>
       </c>
-      <c r="F19" s="243"/>
+      <c r="F19" s="266"/>
       <c r="G19" s="72" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="H19" s="36"/>
       <c r="I19" s="37" t="s">
@@ -4660,11 +4710,11 @@
       <c r="J19" s="95"/>
       <c r="K19" s="29"/>
       <c r="L19" s="44"/>
-      <c r="M19" s="202" t="s">
-        <v>323</v>
-      </c>
-      <c r="O19" s="204" t="s">
-        <v>353</v>
+      <c r="M19" s="199" t="s">
+        <v>335</v>
+      </c>
+      <c r="O19" s="201" t="s">
+        <v>318</v>
       </c>
       <c r="P19" s="6"/>
       <c r="R19" s="6"/>
@@ -4681,7 +4731,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="241"/>
+      <c r="B20" s="264"/>
       <c r="C20" s="79" t="s">
         <v>82</v>
       </c>
@@ -4691,9 +4741,9 @@
       <c r="E20" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="F20" s="237"/>
+      <c r="F20" s="248"/>
       <c r="G20" s="96" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="H20" s="97"/>
       <c r="I20" s="98" t="s">
@@ -4704,12 +4754,12 @@
       <c r="L20" s="101" t="s">
         <v>48</v>
       </c>
-      <c r="M20" s="202" t="s">
-        <v>325</v>
+      <c r="M20" s="199" t="s">
+        <v>336</v>
       </c>
       <c r="N20" s="6"/>
-      <c r="O20" s="204" t="s">
-        <v>354</v>
+      <c r="O20" s="201" t="s">
+        <v>319</v>
       </c>
       <c r="P20" s="6"/>
       <c r="R20" s="6"/>
@@ -4726,7 +4776,7 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B21" s="233" t="s">
+      <c r="B21" s="244" t="s">
         <v>84</v>
       </c>
       <c r="C21" s="102" t="s">
@@ -4738,7 +4788,7 @@
       <c r="E21" s="65" t="s">
         <v>86</v>
       </c>
-      <c r="F21" s="231" t="s">
+      <c r="F21" s="259" t="s">
         <v>27</v>
       </c>
       <c r="G21" s="103" t="s">
@@ -4753,11 +4803,11 @@
       <c r="L21" s="106" t="s">
         <v>88</v>
       </c>
-      <c r="M21" s="202" t="s">
-        <v>334</v>
-      </c>
-      <c r="O21" s="204" t="s">
-        <v>354</v>
+      <c r="M21" s="199" t="s">
+        <v>87</v>
+      </c>
+      <c r="O21" s="201" t="s">
+        <v>319</v>
       </c>
       <c r="P21" s="6"/>
       <c r="R21" s="6"/>
@@ -4774,7 +4824,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22" s="221"/>
+      <c r="B22" s="232"/>
       <c r="C22" s="79" t="s">
         <v>89</v>
       </c>
@@ -4784,7 +4834,7 @@
       <c r="E22" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="F22" s="232"/>
+      <c r="F22" s="260"/>
       <c r="G22" s="107" t="s">
         <v>91</v>
       </c>
@@ -4797,12 +4847,12 @@
       <c r="L22" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="M22" s="202" t="s">
-        <v>348</v>
+      <c r="M22" s="199" t="s">
+        <v>91</v>
       </c>
       <c r="N22" s="6"/>
-      <c r="O22" s="204" t="s">
-        <v>354</v>
+      <c r="O22" s="201" t="s">
+        <v>319</v>
       </c>
       <c r="P22" s="6"/>
       <c r="R22" s="6"/>
@@ -4819,7 +4869,7 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B23" s="233" t="s">
+      <c r="B23" s="244" t="s">
         <v>93</v>
       </c>
       <c r="C23" s="110" t="s">
@@ -4831,11 +4881,11 @@
       <c r="E23" s="65" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="234" t="s">
+      <c r="F23" s="245" t="s">
         <v>27</v>
       </c>
       <c r="G23" s="111" t="s">
-        <v>335</v>
+        <v>315</v>
       </c>
       <c r="H23" s="112"/>
       <c r="I23" s="68" t="s">
@@ -4848,11 +4898,11 @@
       <c r="L23" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="M23" s="202" t="s">
-        <v>336</v>
+      <c r="M23" s="199" t="s">
+        <v>337</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="P23" s="6"/>
       <c r="R23" s="6"/>
@@ -4869,7 +4919,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24" s="221"/>
+      <c r="B24" s="232"/>
       <c r="C24" s="114" t="s">
         <v>99</v>
       </c>
@@ -4879,7 +4929,7 @@
       <c r="E24" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="F24" s="235"/>
+      <c r="F24" s="246"/>
       <c r="G24" s="82" t="s">
         <v>102</v>
       </c>
@@ -4894,12 +4944,12 @@
       <c r="L24" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="M24" s="202" t="s">
-        <v>337</v>
+      <c r="M24" s="199" t="s">
+        <v>102</v>
       </c>
       <c r="N24" s="6"/>
       <c r="O24" s="6" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="P24" s="6"/>
       <c r="R24" s="6"/>
@@ -4916,7 +4966,7 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25" s="233" t="s">
+      <c r="B25" s="244" t="s">
         <v>104</v>
       </c>
       <c r="C25" s="102" t="s">
@@ -4928,7 +4978,7 @@
       <c r="E25" s="65" t="s">
         <v>106</v>
       </c>
-      <c r="F25" s="236" t="s">
+      <c r="F25" s="247" t="s">
         <v>27</v>
       </c>
       <c r="G25" s="111" t="s">
@@ -4942,14 +4992,14 @@
       <c r="K25" s="53" t="s">
         <v>108</v>
       </c>
-      <c r="L25" s="217" t="s">
+      <c r="L25" s="267" t="s">
         <v>109</v>
       </c>
-      <c r="M25" s="202" t="s">
-        <v>338</v>
-      </c>
-      <c r="O25" s="204" t="s">
-        <v>353</v>
+      <c r="M25" s="199" t="s">
+        <v>107</v>
+      </c>
+      <c r="O25" s="201" t="s">
+        <v>318</v>
       </c>
       <c r="P25" s="6"/>
       <c r="R25" s="6"/>
@@ -4966,7 +5016,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26" s="221"/>
+      <c r="B26" s="232"/>
       <c r="C26" s="79" t="s">
         <v>110</v>
       </c>
@@ -4976,7 +5026,7 @@
       <c r="E26" s="56" t="s">
         <v>111</v>
       </c>
-      <c r="F26" s="237"/>
+      <c r="F26" s="248"/>
       <c r="G26" s="82" t="s">
         <v>112</v>
       </c>
@@ -4988,13 +5038,13 @@
       <c r="K26" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="L26" s="218"/>
-      <c r="M26" s="202" t="s">
-        <v>339</v>
+      <c r="L26" s="251"/>
+      <c r="M26" s="199" t="s">
+        <v>112</v>
       </c>
       <c r="N26" s="6"/>
-      <c r="O26" s="204" t="s">
-        <v>353</v>
+      <c r="O26" s="201" t="s">
+        <v>318</v>
       </c>
       <c r="P26" s="6"/>
       <c r="R26" s="6"/>
@@ -5040,12 +5090,12 @@
       <c r="L27" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="M27" s="202" t="s">
-        <v>349</v>
+      <c r="M27" s="199" t="s">
+        <v>116</v>
       </c>
       <c r="N27" s="6"/>
       <c r="O27" s="6" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="P27" s="6"/>
       <c r="Q27" s="6"/>
@@ -5078,8 +5128,8 @@
       <c r="F28" s="127" t="s">
         <v>27</v>
       </c>
-      <c r="G28" s="203" t="s">
-        <v>308</v>
+      <c r="G28" s="200" t="s">
+        <v>305</v>
       </c>
       <c r="H28" s="128"/>
       <c r="I28" s="129" t="s">
@@ -5092,12 +5142,12 @@
       <c r="L28" s="132" t="s">
         <v>120</v>
       </c>
-      <c r="M28" s="202" t="s">
-        <v>350</v>
+      <c r="M28" s="199" t="s">
+        <v>338</v>
       </c>
       <c r="N28" s="6"/>
       <c r="O28" s="6" t="s">
-        <v>355</v>
+        <v>320</v>
       </c>
       <c r="P28" s="6"/>
       <c r="Q28" s="6"/>
@@ -5130,30 +5180,30 @@
       <c r="F29" s="127" t="s">
         <v>27</v>
       </c>
-      <c r="G29" s="219" t="s">
+      <c r="G29" s="268" t="s">
+        <v>316</v>
+      </c>
+      <c r="H29" s="210" t="s">
+        <v>339</v>
+      </c>
+      <c r="I29" s="133" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="134"/>
+      <c r="K29" s="135" t="s">
+        <v>123</v>
+      </c>
+      <c r="L29" s="249" t="s">
+        <v>124</v>
+      </c>
+      <c r="M29" s="254" t="s">
+        <v>316</v>
+      </c>
+      <c r="N29" s="199" t="s">
         <v>340</v>
       </c>
-      <c r="H29" s="133" t="s">
-        <v>123</v>
-      </c>
-      <c r="I29" s="134" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="135"/>
-      <c r="K29" s="136" t="s">
-        <v>124</v>
-      </c>
-      <c r="L29" s="222" t="s">
-        <v>125</v>
-      </c>
-      <c r="M29" s="226" t="s">
-        <v>341</v>
-      </c>
-      <c r="N29" t="s">
-        <v>314</v>
-      </c>
-      <c r="O29" s="204" t="s">
-        <v>352</v>
+      <c r="O29" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P29" s="6"/>
       <c r="Q29" s="6"/>
@@ -5172,38 +5222,38 @@
         <v>28</v>
       </c>
       <c r="B30" s="87" t="s">
+        <v>125</v>
+      </c>
+      <c r="C30" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="C30" s="88" t="s">
+      <c r="D30" s="121" t="s">
         <v>127</v>
       </c>
-      <c r="D30" s="121" t="s">
+      <c r="E30" s="89" t="s">
         <v>128</v>
-      </c>
-      <c r="E30" s="89" t="s">
-        <v>129</v>
       </c>
       <c r="F30" s="127" t="s">
         <v>27</v>
       </c>
-      <c r="G30" s="220"/>
-      <c r="H30" s="137" t="s">
-        <v>130</v>
-      </c>
-      <c r="I30" s="138" t="s">
+      <c r="G30" s="231"/>
+      <c r="H30" s="211" t="s">
+        <v>341</v>
+      </c>
+      <c r="I30" s="136" t="s">
         <v>17</v>
       </c>
-      <c r="J30" s="139"/>
-      <c r="K30" s="140" t="s">
-        <v>124</v>
-      </c>
-      <c r="L30" s="223"/>
-      <c r="M30" s="226"/>
-      <c r="N30" t="s">
-        <v>315</v>
-      </c>
-      <c r="O30" s="204" t="s">
-        <v>352</v>
+      <c r="J30" s="137"/>
+      <c r="K30" s="138" t="s">
+        <v>123</v>
+      </c>
+      <c r="L30" s="250"/>
+      <c r="M30" s="254"/>
+      <c r="N30" s="199" t="s">
+        <v>342</v>
+      </c>
+      <c r="O30" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
@@ -5221,39 +5271,39 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B31" s="233" t="s">
+      <c r="B31" s="244" t="s">
         <v>68</v>
       </c>
       <c r="C31" s="74" t="s">
+        <v>129</v>
+      </c>
+      <c r="D31" s="65" t="s">
+        <v>127</v>
+      </c>
+      <c r="E31" s="75" t="s">
+        <v>130</v>
+      </c>
+      <c r="F31" s="139" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31" s="231"/>
+      <c r="H31" s="140" t="s">
+        <v>343</v>
+      </c>
+      <c r="I31" s="136" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="95"/>
+      <c r="K31" s="141" t="s">
         <v>131</v>
       </c>
-      <c r="D31" s="65" t="s">
-        <v>128</v>
-      </c>
-      <c r="E31" s="75" t="s">
-        <v>132</v>
-      </c>
-      <c r="F31" s="141" t="s">
-        <v>27</v>
-      </c>
-      <c r="G31" s="220"/>
-      <c r="H31" s="142" t="s">
-        <v>133</v>
-      </c>
-      <c r="I31" s="138" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="95"/>
-      <c r="K31" s="143" t="s">
-        <v>134</v>
-      </c>
-      <c r="L31" s="223"/>
-      <c r="M31" s="226"/>
-      <c r="N31" s="202" t="s">
-        <v>319</v>
-      </c>
-      <c r="O31" s="204" t="s">
-        <v>352</v>
+      <c r="L31" s="250"/>
+      <c r="M31" s="254"/>
+      <c r="N31" s="199" t="s">
+        <v>344</v>
+      </c>
+      <c r="O31" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P31" s="6"/>
       <c r="Q31" s="6"/>
@@ -5271,7 +5321,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B32" s="220"/>
+      <c r="B32" s="231"/>
       <c r="C32" s="33" t="s">
         <v>69</v>
       </c>
@@ -5282,24 +5332,24 @@
         <v>71</v>
       </c>
       <c r="F32" s="35"/>
-      <c r="G32" s="220"/>
-      <c r="H32" s="142" t="s">
-        <v>72</v>
-      </c>
-      <c r="I32" s="138" t="s">
+      <c r="G32" s="231"/>
+      <c r="H32" s="140" t="s">
+        <v>306</v>
+      </c>
+      <c r="I32" s="136" t="s">
         <v>17</v>
       </c>
       <c r="J32" s="95"/>
-      <c r="K32" s="143" t="s">
-        <v>124</v>
-      </c>
-      <c r="L32" s="223"/>
-      <c r="M32" s="226"/>
-      <c r="N32" t="s">
+      <c r="K32" s="141" t="s">
+        <v>123</v>
+      </c>
+      <c r="L32" s="250"/>
+      <c r="M32" s="254"/>
+      <c r="N32" s="199" t="s">
+        <v>345</v>
+      </c>
+      <c r="O32" s="201" t="s">
         <v>317</v>
-      </c>
-      <c r="O32" s="204" t="s">
-        <v>352</v>
       </c>
       <c r="P32" s="6"/>
       <c r="Q32" s="6"/>
@@ -5317,35 +5367,35 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B33" s="220"/>
+      <c r="B33" s="231"/>
       <c r="C33" s="33" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D33" s="40" t="s">
         <v>41</v>
       </c>
       <c r="E33" s="40" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F33" s="35"/>
-      <c r="G33" s="220"/>
-      <c r="H33" s="142" t="s">
-        <v>137</v>
-      </c>
-      <c r="I33" s="138" t="s">
+      <c r="G33" s="231"/>
+      <c r="H33" s="140" t="s">
+        <v>346</v>
+      </c>
+      <c r="I33" s="136" t="s">
         <v>46</v>
       </c>
       <c r="J33" s="95"/>
-      <c r="K33" s="143" t="s">
-        <v>138</v>
-      </c>
-      <c r="L33" s="223"/>
-      <c r="M33" s="226"/>
-      <c r="N33" t="s">
+      <c r="K33" s="141" t="s">
+        <v>135</v>
+      </c>
+      <c r="L33" s="250"/>
+      <c r="M33" s="254"/>
+      <c r="N33" s="199" t="s">
+        <v>347</v>
+      </c>
+      <c r="O33" s="201" t="s">
         <v>318</v>
-      </c>
-      <c r="O33" s="204" t="s">
-        <v>353</v>
       </c>
       <c r="P33" s="6"/>
       <c r="Q33" s="6"/>
@@ -5363,37 +5413,37 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B34" s="221"/>
-      <c r="C34" s="144" t="s">
-        <v>139</v>
+      <c r="B34" s="232"/>
+      <c r="C34" s="142" t="s">
+        <v>136</v>
       </c>
       <c r="D34" s="25" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E34" s="25" t="s">
-        <v>141</v>
-      </c>
-      <c r="F34" s="145" t="s">
+        <v>138</v>
+      </c>
+      <c r="F34" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="G34" s="221"/>
+      <c r="G34" s="232"/>
       <c r="H34" s="59" t="s">
-        <v>142</v>
+        <v>348</v>
       </c>
       <c r="I34" s="60" t="s">
         <v>17</v>
       </c>
       <c r="J34" s="119"/>
-      <c r="K34" s="146" t="s">
-        <v>124</v>
-      </c>
-      <c r="L34" s="218"/>
-      <c r="M34" s="227"/>
-      <c r="N34" t="s">
-        <v>316</v>
-      </c>
-      <c r="O34" s="204" t="s">
-        <v>352</v>
+      <c r="K34" s="144" t="s">
+        <v>123</v>
+      </c>
+      <c r="L34" s="251"/>
+      <c r="M34" s="255"/>
+      <c r="N34" s="199" t="s">
+        <v>349</v>
+      </c>
+      <c r="O34" s="201" t="s">
+        <v>317</v>
       </c>
       <c r="P34" s="6"/>
       <c r="Q34" s="6"/>
@@ -5407,18 +5457,18 @@
       <c r="Y34" s="6"/>
     </row>
     <row r="35" spans="1:25" ht="16.5" thickBot="1">
-      <c r="A35" s="147"/>
-      <c r="B35" s="147"/>
-      <c r="C35" s="147"/>
-      <c r="D35" s="148"/>
-      <c r="E35" s="148"/>
-      <c r="F35" s="147"/>
-      <c r="G35" s="147"/>
-      <c r="H35" s="147"/>
-      <c r="I35" s="147"/>
-      <c r="J35" s="148"/>
-      <c r="K35" s="147"/>
-      <c r="L35" s="147"/>
+      <c r="A35" s="145"/>
+      <c r="B35" s="145"/>
+      <c r="C35" s="145"/>
+      <c r="D35" s="146"/>
+      <c r="E35" s="146"/>
+      <c r="F35" s="145"/>
+      <c r="G35" s="145"/>
+      <c r="H35" s="145"/>
+      <c r="I35" s="145"/>
+      <c r="J35" s="146"/>
+      <c r="K35" s="145"/>
+      <c r="L35" s="145"/>
       <c r="M35" s="6"/>
       <c r="P35" s="6"/>
       <c r="Q35" s="6"/>
@@ -5487,7 +5537,16 @@
     </row>
     <row r="38" spans="1:25" ht="16.5" thickBot="1">
       <c r="A38" s="6"/>
-      <c r="J38" s="6"/>
+      <c r="C38" s="215" t="s">
+        <v>350</v>
+      </c>
+      <c r="D38" s="216"/>
+      <c r="E38" s="216"/>
+      <c r="F38" s="216"/>
+      <c r="G38" s="216"/>
+      <c r="H38" s="216"/>
+      <c r="I38" s="216"/>
+      <c r="J38" s="217"/>
       <c r="K38" s="6"/>
       <c r="L38" s="6"/>
       <c r="M38" s="6"/>
@@ -5506,7 +5565,22 @@
     </row>
     <row r="39" spans="1:25" ht="16.5" thickBot="1">
       <c r="A39" s="6"/>
-      <c r="J39" s="6"/>
+      <c r="C39" s="204"/>
+      <c r="D39" s="205" t="s">
+        <v>328</v>
+      </c>
+      <c r="E39" s="206"/>
+      <c r="F39" s="205" t="s">
+        <v>325</v>
+      </c>
+      <c r="G39" s="206"/>
+      <c r="H39" s="206"/>
+      <c r="I39" s="205" t="s">
+        <v>326</v>
+      </c>
+      <c r="J39" s="205" t="s">
+        <v>323</v>
+      </c>
       <c r="K39" s="6"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
@@ -5523,9 +5597,24 @@
       <c r="X39" s="6"/>
       <c r="Y39" s="6"/>
     </row>
-    <row r="40" spans="1:25" ht="16.5" thickBot="1">
+    <row r="40" spans="1:25" ht="33" thickBot="1">
       <c r="A40" s="6"/>
-      <c r="J40" s="6"/>
+      <c r="C40" s="207"/>
+      <c r="D40" s="208" t="s">
+        <v>329</v>
+      </c>
+      <c r="E40" s="209"/>
+      <c r="F40" s="208" t="s">
+        <v>352</v>
+      </c>
+      <c r="G40" s="209"/>
+      <c r="H40" s="209"/>
+      <c r="I40" s="208" t="s">
+        <v>353</v>
+      </c>
+      <c r="J40" s="208" t="s">
+        <v>333</v>
+      </c>
       <c r="K40" s="6"/>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
@@ -5544,7 +5633,22 @@
     </row>
     <row r="41" spans="1:25" ht="16.5" thickBot="1">
       <c r="A41" s="6"/>
-      <c r="J41" s="6"/>
+      <c r="C41" s="207"/>
+      <c r="D41" s="208" t="s">
+        <v>329</v>
+      </c>
+      <c r="E41" s="209"/>
+      <c r="F41" s="208" t="s">
+        <v>351</v>
+      </c>
+      <c r="G41" s="209"/>
+      <c r="H41" s="209"/>
+      <c r="I41" s="208" t="s">
+        <v>330</v>
+      </c>
+      <c r="J41" s="208" t="s">
+        <v>333</v>
+      </c>
       <c r="K41" s="6"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
@@ -10765,16 +10869,11 @@
       <c r="Y234" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="19">
+    <mergeCell ref="G1:I1"/>
     <mergeCell ref="M29:M34"/>
     <mergeCell ref="M1:O1"/>
     <mergeCell ref="F21:F22"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B21:B22"/>
-    <mergeCell ref="B23:B24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="F25:F26"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B3:B9"/>
     <mergeCell ref="B10:B15"/>
@@ -10782,8 +10881,14 @@
     <mergeCell ref="F17:F20"/>
     <mergeCell ref="L25:L26"/>
     <mergeCell ref="G29:G34"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="B31:B34"/>
+    <mergeCell ref="B21:B22"/>
+    <mergeCell ref="B23:B24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="F25:F26"/>
+    <mergeCell ref="C38:J38"/>
     <mergeCell ref="L29:L34"/>
-    <mergeCell ref="G1:I1"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -10814,315 +10919,315 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="16.5" thickBot="1">
-      <c r="A1" s="149"/>
-      <c r="B1" s="262" t="s">
+      <c r="A1" s="147"/>
+      <c r="B1" s="239" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="263"/>
-      <c r="D1" s="264" t="s">
+      <c r="C1" s="240"/>
+      <c r="D1" s="241" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="242"/>
+      <c r="F1" s="242"/>
+      <c r="G1" s="242"/>
+      <c r="H1" s="243"/>
+      <c r="I1" s="148" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1" s="237" t="s">
+        <v>307</v>
+      </c>
+      <c r="K1" s="238"/>
+      <c r="L1" s="238"/>
+      <c r="O1" s="203"/>
+    </row>
+    <row r="2" spans="1:15" ht="27.75" thickBot="1">
+      <c r="A2" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="151" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="152" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="266"/>
-      <c r="I1" s="150" t="s">
+      <c r="E2" s="153" t="s">
         <v>144</v>
       </c>
-      <c r="J1" s="244" t="s">
-        <v>310</v>
-      </c>
-      <c r="K1" s="245"/>
-      <c r="L1" s="245"/>
-      <c r="O1" s="207"/>
-    </row>
-    <row r="2" spans="1:15" ht="27.75" thickBot="1">
-      <c r="A2" s="151" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="152" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="153" t="s">
+      <c r="F2" s="153" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="153" t="s">
         <v>145</v>
       </c>
-      <c r="D2" s="154" t="s">
-        <v>146</v>
-      </c>
-      <c r="E2" s="155" t="s">
-        <v>147</v>
-      </c>
-      <c r="F2" s="155" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="155" t="s">
-        <v>148</v>
-      </c>
-      <c r="H2" s="156" t="s">
+      <c r="H2" s="154" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="157"/>
+      <c r="I2" s="155"/>
       <c r="J2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="K2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="L2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="41.25" thickBot="1">
-      <c r="A3" s="151">
+      <c r="A3" s="149">
         <f t="shared" ref="A3:A70" si="0">ROW()-2</f>
         <v>1</v>
       </c>
-      <c r="B3" s="158" t="s">
-        <v>149</v>
-      </c>
-      <c r="C3" s="159"/>
-      <c r="D3" s="160" t="s">
+      <c r="B3" s="156" t="s">
+        <v>146</v>
+      </c>
+      <c r="C3" s="157"/>
+      <c r="D3" s="158" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="92"/>
-      <c r="F3" s="161" t="s">
-        <v>150</v>
-      </c>
-      <c r="G3" s="161" t="s">
+      <c r="F3" s="159" t="s">
+        <v>147</v>
+      </c>
+      <c r="G3" s="159" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="162"/>
-      <c r="I3" s="163"/>
-      <c r="J3" s="202" t="s">
-        <v>365</v>
+      <c r="H3" s="160"/>
+      <c r="I3" s="161"/>
+      <c r="J3" s="199" t="s">
+        <v>330</v>
       </c>
       <c r="L3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="54.75" thickBot="1">
-      <c r="A4" s="151">
+      <c r="A4" s="149">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B4" s="164" t="s">
-        <v>151</v>
-      </c>
-      <c r="C4" s="159"/>
-      <c r="D4" s="165" t="s">
-        <v>357</v>
+      <c r="B4" s="162" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="157"/>
+      <c r="D4" s="163" t="s">
+        <v>322</v>
       </c>
       <c r="E4" s="123"/>
       <c r="F4" s="124" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G4" s="124" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="155"/>
-      <c r="I4" s="157"/>
+      <c r="H4" s="153"/>
+      <c r="I4" s="155"/>
       <c r="J4" t="s">
         <v>52</v>
       </c>
       <c r="L4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="16.5" thickBot="1">
-      <c r="A5" s="151">
+      <c r="A5" s="149">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="260" t="s">
+      <c r="B5" s="235" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="139" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="233" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="94" t="s">
         <v>152</v>
       </c>
-      <c r="C5" s="141" t="s">
+      <c r="F5" s="164" t="s">
+        <v>147</v>
+      </c>
+      <c r="G5" s="164" t="s">
         <v>153</v>
       </c>
-      <c r="D5" s="259" t="s">
-        <v>154</v>
-      </c>
-      <c r="E5" s="94" t="s">
-        <v>155</v>
-      </c>
-      <c r="F5" s="166" t="s">
-        <v>150</v>
-      </c>
-      <c r="G5" s="166" t="s">
-        <v>156</v>
-      </c>
       <c r="H5" s="118"/>
-      <c r="I5" s="167"/>
-      <c r="J5" s="248" t="s">
-        <v>154</v>
+      <c r="I5" s="165"/>
+      <c r="J5" s="220" t="s">
+        <v>151</v>
       </c>
       <c r="K5" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="L5" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="27.75" thickBot="1">
-      <c r="A6" s="151">
+      <c r="A6" s="149">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="255"/>
+      <c r="B6" s="228"/>
       <c r="C6" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="255"/>
+      <c r="D6" s="228"/>
       <c r="E6" s="36" t="s">
         <v>22</v>
       </c>
       <c r="F6" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G6" s="37" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="95"/>
-      <c r="I6" s="168"/>
-      <c r="J6" s="248"/>
+      <c r="I6" s="166"/>
+      <c r="J6" s="220"/>
       <c r="K6" t="s">
         <v>22</v>
       </c>
       <c r="L6" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="16.5" thickBot="1">
-      <c r="A7" s="151">
+      <c r="A7" s="149">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="255"/>
+      <c r="B7" s="228"/>
       <c r="C7" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="255"/>
+      <c r="D7" s="228"/>
       <c r="E7" s="36" t="s">
         <v>28</v>
       </c>
       <c r="F7" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G7" s="37" t="s">
         <v>25</v>
       </c>
       <c r="H7" s="95"/>
-      <c r="I7" s="168"/>
-      <c r="J7" s="248"/>
+      <c r="I7" s="166"/>
+      <c r="J7" s="220"/>
       <c r="K7" t="s">
         <v>28</v>
       </c>
       <c r="L7" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:15" ht="16.5" thickBot="1">
-      <c r="A8" s="151">
+      <c r="A8" s="149">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="255"/>
+      <c r="B8" s="228"/>
       <c r="C8" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="255"/>
+      <c r="D8" s="228"/>
       <c r="E8" s="36" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G8" s="37" t="s">
         <v>31</v>
       </c>
       <c r="H8" s="95"/>
-      <c r="I8" s="168"/>
-      <c r="J8" s="248"/>
+      <c r="I8" s="166"/>
+      <c r="J8" s="220"/>
       <c r="K8" t="s">
         <v>33</v>
       </c>
       <c r="L8" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="9" spans="1:15" ht="16.5" thickBot="1">
-      <c r="A9" s="151">
+      <c r="A9" s="149">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="255"/>
+      <c r="B9" s="228"/>
       <c r="C9" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="255"/>
+      <c r="D9" s="228"/>
       <c r="E9" s="36" t="s">
         <v>37</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G9" s="37" t="s">
         <v>35</v>
       </c>
       <c r="H9" s="95"/>
-      <c r="I9" s="168"/>
-      <c r="J9" s="248"/>
+      <c r="I9" s="166"/>
+      <c r="J9" s="220"/>
       <c r="K9" t="s">
         <v>37</v>
       </c>
       <c r="L9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10" spans="1:15" ht="27.75" thickBot="1">
-      <c r="A10" s="151">
+      <c r="A10" s="149">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="255"/>
+      <c r="B10" s="228"/>
       <c r="C10" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="255"/>
+      <c r="D10" s="228"/>
       <c r="E10" s="36" t="s">
         <v>43</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G10" s="37" t="s">
         <v>41</v>
       </c>
       <c r="H10" s="95"/>
-      <c r="I10" s="168"/>
-      <c r="J10" s="248"/>
+      <c r="I10" s="166"/>
+      <c r="J10" s="220"/>
       <c r="K10" t="s">
         <v>43</v>
       </c>
       <c r="L10" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" spans="1:15" ht="27.75" thickBot="1">
-      <c r="A11" s="151">
+      <c r="A11" s="149">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="255"/>
+      <c r="B11" s="228"/>
       <c r="C11" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="D11" s="255"/>
+        <v>155</v>
+      </c>
+      <c r="D11" s="228"/>
       <c r="E11" s="36" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F11" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G11" s="37" t="s">
         <v>41</v>
@@ -11130,61 +11235,61 @@
       <c r="H11" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="168"/>
-      <c r="J11" s="248"/>
+      <c r="I11" s="166"/>
+      <c r="J11" s="220"/>
       <c r="K11" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="L11" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="27.75" thickBot="1">
-      <c r="A12" s="151">
+      <c r="A12" s="149">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="255"/>
+      <c r="B12" s="228"/>
       <c r="C12" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="D12" s="255"/>
+        <v>157</v>
+      </c>
+      <c r="D12" s="228"/>
       <c r="E12" s="36" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G12" s="37" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="H12" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="168"/>
-      <c r="J12" s="248"/>
+      <c r="I12" s="166"/>
+      <c r="J12" s="220"/>
       <c r="K12" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:15" ht="27.75" thickBot="1">
-      <c r="A13" s="151">
+      <c r="A13" s="149">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="255"/>
+      <c r="B13" s="228"/>
       <c r="C13" s="35" t="s">
-        <v>163</v>
-      </c>
-      <c r="D13" s="255"/>
+        <v>160</v>
+      </c>
+      <c r="D13" s="228"/>
       <c r="E13" s="36" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G13" s="37" t="s">
         <v>70</v>
@@ -11192,206 +11297,206 @@
       <c r="H13" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="168"/>
-      <c r="J13" s="248"/>
+      <c r="I13" s="166"/>
+      <c r="J13" s="220"/>
       <c r="K13" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:15" ht="27.75" thickBot="1">
-      <c r="A14" s="151">
+      <c r="A14" s="149">
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="B14" s="255"/>
+      <c r="B14" s="228"/>
       <c r="C14" s="35" t="s">
-        <v>165</v>
-      </c>
-      <c r="D14" s="255"/>
+        <v>162</v>
+      </c>
+      <c r="D14" s="228"/>
       <c r="E14" s="36" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F14" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G14" s="37" t="s">
         <v>41</v>
       </c>
       <c r="H14" s="95"/>
-      <c r="I14" s="168"/>
-      <c r="J14" s="248"/>
+      <c r="I14" s="166"/>
+      <c r="J14" s="220"/>
       <c r="K14" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="L14" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="27.75" thickBot="1">
-      <c r="A15" s="151">
+      <c r="A15" s="149">
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="B15" s="255"/>
+      <c r="B15" s="228"/>
       <c r="C15" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="D15" s="255"/>
+        <v>164</v>
+      </c>
+      <c r="D15" s="228"/>
       <c r="E15" s="36" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F15" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G15" s="37" t="s">
         <v>41</v>
       </c>
       <c r="H15" s="95"/>
-      <c r="I15" s="168"/>
-      <c r="J15" s="248"/>
+      <c r="I15" s="166"/>
+      <c r="J15" s="220"/>
       <c r="K15" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="L15" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="27.75" thickBot="1">
-      <c r="A16" s="151">
+      <c r="A16" s="149">
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="B16" s="255"/>
+      <c r="B16" s="228"/>
       <c r="C16" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="D16" s="255"/>
+        <v>166</v>
+      </c>
+      <c r="D16" s="228"/>
       <c r="E16" s="36" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G16" s="37" t="s">
         <v>41</v>
       </c>
       <c r="H16" s="95"/>
-      <c r="I16" s="168"/>
-      <c r="J16" s="248"/>
+      <c r="I16" s="166"/>
+      <c r="J16" s="220"/>
       <c r="K16" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="L16" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A17" s="151">
+      <c r="A17" s="149">
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="B17" s="255"/>
+      <c r="B17" s="228"/>
       <c r="C17" s="35" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="255"/>
+      <c r="D17" s="228"/>
       <c r="E17" s="36" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G17" s="37" t="s">
         <v>41</v>
       </c>
       <c r="H17" s="95"/>
-      <c r="I17" s="168"/>
-      <c r="J17" s="248"/>
+      <c r="I17" s="166"/>
+      <c r="J17" s="220"/>
       <c r="K17" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="L17" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="18" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A18" s="151">
+      <c r="A18" s="149">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="B18" s="255"/>
+      <c r="B18" s="228"/>
       <c r="C18" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="D18" s="255"/>
+      <c r="D18" s="228"/>
       <c r="E18" s="36" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F18" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G18" s="37" t="s">
         <v>14</v>
       </c>
       <c r="H18" s="95"/>
-      <c r="I18" s="168"/>
-      <c r="J18" s="248"/>
+      <c r="I18" s="166"/>
+      <c r="J18" s="220"/>
       <c r="K18" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="L18" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A19" s="151">
+      <c r="A19" s="149">
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="B19" s="255"/>
+      <c r="B19" s="228"/>
       <c r="C19" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="D19" s="255"/>
+        <v>170</v>
+      </c>
+      <c r="D19" s="228"/>
       <c r="E19" s="36" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F19" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G19" s="37" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H19" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="168"/>
-      <c r="J19" s="248"/>
+      <c r="I19" s="166"/>
+      <c r="J19" s="220"/>
       <c r="K19" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="L19" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A20" s="151">
+      <c r="A20" s="149">
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B20" s="256"/>
-      <c r="C20" s="169" t="s">
-        <v>176</v>
-      </c>
-      <c r="D20" s="258"/>
+      <c r="B20" s="229"/>
+      <c r="C20" s="167" t="s">
+        <v>173</v>
+      </c>
+      <c r="D20" s="234"/>
       <c r="E20" s="83" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F20" s="84" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G20" s="84" t="s">
         <v>14</v>
@@ -11399,210 +11504,210 @@
       <c r="H20" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="I20" s="170"/>
-      <c r="J20" s="248"/>
+      <c r="I20" s="168"/>
+      <c r="J20" s="220"/>
       <c r="K20" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="L20" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A21" s="151">
+      <c r="A21" s="149">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="B21" s="254" t="s">
-        <v>178</v>
-      </c>
-      <c r="C21" s="171" t="s">
+      <c r="B21" s="227" t="s">
+        <v>175</v>
+      </c>
+      <c r="C21" s="169" t="s">
         <v>53</v>
       </c>
-      <c r="D21" s="261" t="s">
-        <v>179</v>
+      <c r="D21" s="236" t="s">
+        <v>176</v>
       </c>
       <c r="E21" s="94" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="166" t="s">
-        <v>150</v>
+      <c r="F21" s="164" t="s">
+        <v>147</v>
       </c>
       <c r="G21" s="118" t="s">
         <v>31</v>
       </c>
       <c r="H21" s="118"/>
-      <c r="I21" s="167"/>
-      <c r="J21" s="248" t="s">
-        <v>179</v>
+      <c r="I21" s="165"/>
+      <c r="J21" s="220" t="s">
+        <v>176</v>
       </c>
       <c r="K21" t="s">
         <v>55</v>
       </c>
       <c r="L21" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A22" s="151">
+      <c r="A22" s="149">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="B22" s="255"/>
+      <c r="B22" s="228"/>
       <c r="C22" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="D22" s="255"/>
+      <c r="D22" s="228"/>
       <c r="E22" s="36" t="s">
         <v>58</v>
       </c>
       <c r="F22" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G22" s="95" t="s">
         <v>35</v>
       </c>
       <c r="H22" s="95"/>
-      <c r="I22" s="168"/>
-      <c r="J22" s="248"/>
+      <c r="I22" s="166"/>
+      <c r="J22" s="220"/>
       <c r="K22" t="s">
         <v>58</v>
       </c>
       <c r="L22" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A23" s="151">
+      <c r="A23" s="149">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="B23" s="255"/>
+      <c r="B23" s="228"/>
       <c r="C23" s="35" t="s">
         <v>59</v>
       </c>
-      <c r="D23" s="255"/>
+      <c r="D23" s="228"/>
       <c r="E23" s="36" t="s">
         <v>61</v>
       </c>
       <c r="F23" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G23" s="95" t="s">
         <v>31</v>
       </c>
       <c r="H23" s="95"/>
-      <c r="I23" s="168"/>
-      <c r="J23" s="248"/>
+      <c r="I23" s="166"/>
+      <c r="J23" s="220"/>
       <c r="K23" t="s">
         <v>61</v>
       </c>
       <c r="L23" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A24" s="151">
+      <c r="A24" s="149">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="B24" s="255"/>
+      <c r="B24" s="228"/>
       <c r="C24" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="D24" s="255"/>
+      <c r="D24" s="228"/>
       <c r="E24" s="36" t="s">
         <v>64</v>
       </c>
       <c r="F24" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G24" s="95" t="s">
         <v>31</v>
       </c>
       <c r="H24" s="95"/>
-      <c r="I24" s="168"/>
-      <c r="J24" s="248"/>
+      <c r="I24" s="166"/>
+      <c r="J24" s="220"/>
       <c r="K24" t="s">
         <v>64</v>
       </c>
       <c r="L24" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A25" s="151">
+      <c r="A25" s="149">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="B25" s="255"/>
+      <c r="B25" s="228"/>
       <c r="C25" s="35" t="s">
-        <v>180</v>
-      </c>
-      <c r="D25" s="255"/>
+        <v>177</v>
+      </c>
+      <c r="D25" s="228"/>
       <c r="E25" s="36" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F25" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G25" s="95" t="s">
         <v>35</v>
       </c>
       <c r="H25" s="95"/>
-      <c r="I25" s="168"/>
-      <c r="J25" s="248"/>
+      <c r="I25" s="166"/>
+      <c r="J25" s="220"/>
       <c r="K25" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="L25" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:12" ht="26.25" thickBot="1">
-      <c r="A26" s="151">
+      <c r="A26" s="149">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="B26" s="255"/>
+      <c r="B26" s="228"/>
       <c r="C26" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="255"/>
+      <c r="D26" s="228"/>
       <c r="E26" s="36" t="s">
         <v>67</v>
       </c>
       <c r="F26" s="95" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G26" s="95" t="s">
         <v>41</v>
       </c>
       <c r="H26" s="95"/>
-      <c r="I26" s="168"/>
-      <c r="J26" s="248"/>
+      <c r="I26" s="166"/>
+      <c r="J26" s="220"/>
       <c r="K26" t="s">
         <v>67</v>
       </c>
       <c r="L26" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A27" s="151">
+      <c r="A27" s="149">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="B27" s="255"/>
+      <c r="B27" s="228"/>
       <c r="C27" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="D27" s="255"/>
+        <v>179</v>
+      </c>
+      <c r="D27" s="228"/>
       <c r="E27" s="36" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F27" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G27" s="95" t="s">
         <v>75</v>
@@ -11610,119 +11715,119 @@
       <c r="H27" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I27" s="168"/>
-      <c r="J27" s="248"/>
+      <c r="I27" s="166"/>
+      <c r="J27" s="220"/>
       <c r="K27" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="L27" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="26.25" thickBot="1">
-      <c r="A28" s="151">
+      <c r="A28" s="149">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="B28" s="255"/>
+      <c r="B28" s="228"/>
       <c r="C28" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="D28" s="255"/>
+        <v>181</v>
+      </c>
+      <c r="D28" s="228"/>
       <c r="E28" s="36" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F28" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G28" s="95" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H28" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I28" s="168"/>
-      <c r="J28" s="248"/>
+      <c r="I28" s="166"/>
+      <c r="J28" s="220"/>
       <c r="K28" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="L28" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:12" ht="26.25" thickBot="1">
-      <c r="A29" s="151">
+      <c r="A29" s="149">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="B29" s="255"/>
+      <c r="B29" s="228"/>
       <c r="C29" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="D29" s="255"/>
+        <v>184</v>
+      </c>
+      <c r="D29" s="228"/>
       <c r="E29" s="36" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F29" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G29" s="95" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H29" s="95"/>
-      <c r="I29" s="168"/>
-      <c r="J29" s="248"/>
+      <c r="I29" s="166"/>
+      <c r="J29" s="220"/>
       <c r="K29" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="L29" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="26.25" thickBot="1">
-      <c r="A30" s="151">
+      <c r="A30" s="149">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="B30" s="255"/>
+      <c r="B30" s="228"/>
       <c r="C30" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="D30" s="255"/>
+        <v>186</v>
+      </c>
+      <c r="D30" s="228"/>
       <c r="E30" s="36" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F30" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G30" s="95" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H30" s="95"/>
-      <c r="I30" s="168"/>
-      <c r="J30" s="248"/>
+      <c r="I30" s="166"/>
+      <c r="J30" s="220"/>
       <c r="K30" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="L30" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A31" s="151">
+      <c r="A31" s="149">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="B31" s="255"/>
+      <c r="B31" s="228"/>
       <c r="C31" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="D31" s="255"/>
+        <v>188</v>
+      </c>
+      <c r="D31" s="228"/>
       <c r="E31" s="36" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="F31" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G31" s="95" t="s">
         <v>75</v>
@@ -11730,92 +11835,92 @@
       <c r="H31" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I31" s="168"/>
-      <c r="J31" s="248"/>
+      <c r="I31" s="166"/>
+      <c r="J31" s="220"/>
       <c r="K31" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="L31" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="26.25" thickBot="1">
-      <c r="A32" s="151">
+      <c r="A32" s="149">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="B32" s="255"/>
+      <c r="B32" s="228"/>
       <c r="C32" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="D32" s="255"/>
+        <v>190</v>
+      </c>
+      <c r="D32" s="228"/>
       <c r="E32" s="36" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F32" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G32" s="95" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H32" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I32" s="168"/>
-      <c r="J32" s="248"/>
+      <c r="I32" s="166"/>
+      <c r="J32" s="220"/>
       <c r="K32" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="L32" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A33" s="151">
+      <c r="A33" s="149">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="B33" s="255"/>
+      <c r="B33" s="228"/>
       <c r="C33" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="D33" s="255"/>
+        <v>193</v>
+      </c>
+      <c r="D33" s="228"/>
       <c r="E33" s="36" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F33" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G33" s="95" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H33" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I33" s="168"/>
-      <c r="J33" s="248"/>
+      <c r="I33" s="166"/>
+      <c r="J33" s="220"/>
       <c r="K33" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="L33" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A34" s="151">
+      <c r="A34" s="149">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="B34" s="256"/>
-      <c r="C34" s="169" t="s">
-        <v>199</v>
-      </c>
-      <c r="D34" s="258"/>
+      <c r="B34" s="229"/>
+      <c r="C34" s="167" t="s">
+        <v>196</v>
+      </c>
+      <c r="D34" s="234"/>
       <c r="E34" s="115" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F34" s="48" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G34" s="116" t="s">
         <v>35</v>
@@ -11823,253 +11928,253 @@
       <c r="H34" s="116" t="s">
         <v>27</v>
       </c>
-      <c r="I34" s="170"/>
-      <c r="J34" s="248"/>
+      <c r="I34" s="168"/>
+      <c r="J34" s="220"/>
       <c r="K34" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="L34" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="35" spans="1:12" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A35" s="151">
+      <c r="A35" s="149">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="B35" s="254" t="s">
-        <v>201</v>
-      </c>
-      <c r="C35" s="171" t="s">
+      <c r="B35" s="227" t="s">
+        <v>198</v>
+      </c>
+      <c r="C35" s="169" t="s">
         <v>69</v>
       </c>
-      <c r="D35" s="259" t="s">
-        <v>202</v>
+      <c r="D35" s="233" t="s">
+        <v>199</v>
       </c>
       <c r="E35" s="112" t="s">
         <v>72</v>
       </c>
       <c r="F35" s="68" t="s">
-        <v>150</v>
-      </c>
-      <c r="G35" s="166" t="s">
+        <v>147</v>
+      </c>
+      <c r="G35" s="164" t="s">
         <v>70</v>
       </c>
       <c r="H35" s="118"/>
-      <c r="I35" s="167"/>
-      <c r="J35" s="246" t="s">
-        <v>202</v>
+      <c r="I35" s="165"/>
+      <c r="J35" s="218" t="s">
+        <v>199</v>
       </c>
       <c r="K35" t="s">
         <v>72</v>
       </c>
       <c r="L35" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="36" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A36" s="151">
+      <c r="A36" s="149">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="B36" s="255"/>
+      <c r="B36" s="228"/>
       <c r="C36" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="D36" s="255"/>
+        <v>132</v>
+      </c>
+      <c r="D36" s="228"/>
       <c r="E36" s="36" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F36" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G36" s="37" t="s">
         <v>41</v>
       </c>
       <c r="H36" s="95"/>
-      <c r="I36" s="168"/>
-      <c r="J36" s="249"/>
+      <c r="I36" s="166"/>
+      <c r="J36" s="221"/>
       <c r="K36" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="L36" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A37" s="151">
+      <c r="A37" s="149">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="B37" s="255"/>
+      <c r="B37" s="228"/>
       <c r="C37" s="35" t="s">
-        <v>203</v>
-      </c>
-      <c r="D37" s="255"/>
+        <v>200</v>
+      </c>
+      <c r="D37" s="228"/>
       <c r="E37" s="36" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F37" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G37" s="37" t="s">
         <v>41</v>
       </c>
       <c r="H37" s="95"/>
-      <c r="I37" s="168"/>
-      <c r="J37" s="249"/>
+      <c r="I37" s="166"/>
+      <c r="J37" s="221"/>
       <c r="K37" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="L37" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="38" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A38" s="151">
+      <c r="A38" s="149">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="B38" s="255"/>
+      <c r="B38" s="228"/>
       <c r="C38" s="35" t="s">
-        <v>205</v>
-      </c>
-      <c r="D38" s="255"/>
-      <c r="E38" s="142" t="s">
-        <v>206</v>
-      </c>
-      <c r="F38" s="138" t="s">
-        <v>157</v>
-      </c>
-      <c r="G38" s="138" t="s">
+        <v>202</v>
+      </c>
+      <c r="D38" s="228"/>
+      <c r="E38" s="140" t="s">
+        <v>203</v>
+      </c>
+      <c r="F38" s="136" t="s">
+        <v>154</v>
+      </c>
+      <c r="G38" s="136" t="s">
         <v>41</v>
       </c>
       <c r="H38" s="95"/>
-      <c r="I38" s="172" t="s">
-        <v>207</v>
-      </c>
-      <c r="J38" s="249"/>
+      <c r="I38" s="170" t="s">
+        <v>204</v>
+      </c>
+      <c r="J38" s="221"/>
       <c r="K38" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="L38" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="39" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A39" s="151">
+      <c r="A39" s="149">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="B39" s="255"/>
+      <c r="B39" s="228"/>
       <c r="C39" s="35" t="s">
-        <v>208</v>
-      </c>
-      <c r="D39" s="255"/>
+        <v>205</v>
+      </c>
+      <c r="D39" s="228"/>
       <c r="E39" s="36" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="F39" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G39" s="37" t="s">
         <v>41</v>
       </c>
       <c r="H39" s="95"/>
-      <c r="I39" s="168"/>
-      <c r="J39" s="249"/>
+      <c r="I39" s="166"/>
+      <c r="J39" s="221"/>
       <c r="K39" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="L39" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="40" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A40" s="151">
+      <c r="A40" s="149">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="B40" s="256"/>
-      <c r="C40" s="145" t="s">
+      <c r="B40" s="229"/>
+      <c r="C40" s="143" t="s">
+        <v>136</v>
+      </c>
+      <c r="D40" s="234"/>
+      <c r="E40" s="115" t="s">
         <v>139</v>
       </c>
-      <c r="D40" s="258"/>
-      <c r="E40" s="115" t="s">
-        <v>142</v>
-      </c>
       <c r="F40" s="48" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G40" s="48" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="H40" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="I40" s="173"/>
-      <c r="J40" s="247"/>
+      <c r="I40" s="171"/>
+      <c r="J40" s="222"/>
       <c r="K40" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="L40" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="51.75" thickBot="1">
-      <c r="A41" s="151">
+      <c r="A41" s="149">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="B41" s="174" t="s">
+      <c r="B41" s="172" t="s">
+        <v>207</v>
+      </c>
+      <c r="C41" s="90" t="s">
+        <v>208</v>
+      </c>
+      <c r="D41" s="173" t="s">
+        <v>209</v>
+      </c>
+      <c r="E41" s="123" t="s">
         <v>210</v>
       </c>
-      <c r="C41" s="90" t="s">
-        <v>211</v>
-      </c>
-      <c r="D41" s="175" t="s">
-        <v>212</v>
-      </c>
-      <c r="E41" s="123" t="s">
-        <v>213</v>
-      </c>
-      <c r="F41" s="176" t="s">
-        <v>157</v>
-      </c>
-      <c r="G41" s="176" t="s">
+      <c r="F41" s="174" t="s">
+        <v>154</v>
+      </c>
+      <c r="G41" s="174" t="s">
         <v>41</v>
       </c>
-      <c r="H41" s="177"/>
-      <c r="I41" s="178"/>
-      <c r="J41" s="205" t="s">
-        <v>212</v>
+      <c r="H41" s="175"/>
+      <c r="I41" s="176"/>
+      <c r="J41" s="202" t="s">
+        <v>209</v>
       </c>
       <c r="K41" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="L41" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="42" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A42" s="151">
+      <c r="A42" s="149">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="B42" s="260" t="s">
+      <c r="B42" s="235" t="s">
+        <v>211</v>
+      </c>
+      <c r="C42" s="139" t="s">
+        <v>212</v>
+      </c>
+      <c r="D42" s="233" t="s">
+        <v>213</v>
+      </c>
+      <c r="E42" s="94" t="s">
         <v>214</v>
       </c>
-      <c r="C42" s="141" t="s">
-        <v>215</v>
-      </c>
-      <c r="D42" s="259" t="s">
-        <v>216</v>
-      </c>
-      <c r="E42" s="94" t="s">
-        <v>217</v>
-      </c>
       <c r="F42" s="68" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G42" s="68" t="s">
         <v>14</v>
@@ -12077,32 +12182,32 @@
       <c r="H42" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="I42" s="179"/>
-      <c r="J42" s="246" t="s">
-        <v>216</v>
+      <c r="I42" s="177"/>
+      <c r="J42" s="218" t="s">
+        <v>213</v>
       </c>
       <c r="K42" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="L42" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="43" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A43" s="151">
+      <c r="A43" s="149">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="B43" s="255"/>
+      <c r="B43" s="228"/>
       <c r="C43" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="D43" s="255"/>
+      <c r="D43" s="228"/>
       <c r="E43" s="36" t="s">
         <v>77</v>
       </c>
       <c r="F43" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G43" s="37" t="s">
         <v>75</v>
@@ -12110,30 +12215,30 @@
       <c r="H43" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I43" s="168"/>
-      <c r="J43" s="249"/>
+      <c r="I43" s="166"/>
+      <c r="J43" s="221"/>
       <c r="K43" t="s">
         <v>77</v>
       </c>
       <c r="L43" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="44" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A44" s="151">
+      <c r="A44" s="149">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="B44" s="255"/>
+      <c r="B44" s="228"/>
       <c r="C44" s="35" t="s">
         <v>78</v>
       </c>
-      <c r="D44" s="255"/>
+      <c r="D44" s="228"/>
       <c r="E44" s="36" t="s">
         <v>80</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G44" s="37" t="s">
         <v>31</v>
@@ -12141,30 +12246,30 @@
       <c r="H44" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I44" s="168"/>
-      <c r="J44" s="249"/>
+      <c r="I44" s="166"/>
+      <c r="J44" s="221"/>
       <c r="K44" t="s">
         <v>80</v>
       </c>
       <c r="L44" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="45" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A45" s="151">
+      <c r="A45" s="149">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="B45" s="255"/>
+      <c r="B45" s="228"/>
       <c r="C45" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="D45" s="255"/>
+        <v>215</v>
+      </c>
+      <c r="D45" s="228"/>
       <c r="E45" s="36" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G45" s="37" t="s">
         <v>31</v>
@@ -12172,30 +12277,30 @@
       <c r="H45" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I45" s="168"/>
-      <c r="J45" s="249"/>
+      <c r="I45" s="166"/>
+      <c r="J45" s="221"/>
       <c r="K45" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="L45" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="46" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A46" s="151">
+      <c r="A46" s="149">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="B46" s="255"/>
+      <c r="B46" s="228"/>
       <c r="C46" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="D46" s="255"/>
+        <v>217</v>
+      </c>
+      <c r="D46" s="228"/>
       <c r="E46" s="36" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F46" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G46" s="37" t="s">
         <v>95</v>
@@ -12203,30 +12308,30 @@
       <c r="H46" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I46" s="168"/>
-      <c r="J46" s="249"/>
+      <c r="I46" s="166"/>
+      <c r="J46" s="221"/>
       <c r="K46" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="L46" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="47" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A47" s="151">
+      <c r="A47" s="149">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="B47" s="255"/>
+      <c r="B47" s="228"/>
       <c r="C47" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="D47" s="255"/>
+        <v>219</v>
+      </c>
+      <c r="D47" s="228"/>
       <c r="E47" s="36" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F47" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G47" s="37" t="s">
         <v>25</v>
@@ -12234,92 +12339,92 @@
       <c r="H47" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I47" s="168"/>
-      <c r="J47" s="249"/>
+      <c r="I47" s="166"/>
+      <c r="J47" s="221"/>
       <c r="K47" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="L47" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="48" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A48" s="151">
+      <c r="A48" s="149">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="B48" s="255"/>
+      <c r="B48" s="228"/>
       <c r="C48" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="D48" s="255"/>
+      <c r="D48" s="228"/>
       <c r="E48" s="36" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F48" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G48" s="37" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H48" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I48" s="168"/>
-      <c r="J48" s="249"/>
+      <c r="I48" s="166"/>
+      <c r="J48" s="221"/>
       <c r="K48" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="L48" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A49" s="151">
+      <c r="A49" s="149">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="B49" s="255"/>
+      <c r="B49" s="228"/>
       <c r="C49" s="35" t="s">
-        <v>226</v>
-      </c>
-      <c r="D49" s="255"/>
+        <v>223</v>
+      </c>
+      <c r="D49" s="228"/>
       <c r="E49" s="36" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F49" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G49" s="37" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H49" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I49" s="168"/>
-      <c r="J49" s="249"/>
+      <c r="I49" s="166"/>
+      <c r="J49" s="221"/>
       <c r="K49" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L49" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A50" s="151">
+      <c r="A50" s="149">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="B50" s="255"/>
+      <c r="B50" s="228"/>
       <c r="C50" s="35" t="s">
-        <v>229</v>
-      </c>
-      <c r="D50" s="255"/>
+        <v>226</v>
+      </c>
+      <c r="D50" s="228"/>
       <c r="E50" s="36" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F50" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G50" s="37" t="s">
         <v>31</v>
@@ -12327,30 +12432,30 @@
       <c r="H50" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I50" s="168"/>
-      <c r="J50" s="249"/>
+      <c r="I50" s="166"/>
+      <c r="J50" s="221"/>
       <c r="K50" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="L50" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A51" s="151">
+      <c r="A51" s="149">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="B51" s="256"/>
-      <c r="C51" s="169" t="s">
-        <v>231</v>
-      </c>
-      <c r="D51" s="258"/>
+      <c r="B51" s="229"/>
+      <c r="C51" s="167" t="s">
+        <v>228</v>
+      </c>
+      <c r="D51" s="234"/>
       <c r="E51" s="115" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F51" s="84" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G51" s="48" t="s">
         <v>35</v>
@@ -12358,36 +12463,36 @@
       <c r="H51" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="I51" s="180" t="s">
-        <v>233</v>
-      </c>
-      <c r="J51" s="247"/>
+      <c r="I51" s="178" t="s">
+        <v>230</v>
+      </c>
+      <c r="J51" s="222"/>
       <c r="K51" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="L51" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A52" s="151">
+      <c r="A52" s="149">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="B52" s="254" t="s">
-        <v>234</v>
-      </c>
-      <c r="C52" s="171" t="s">
-        <v>235</v>
-      </c>
-      <c r="D52" s="259" t="s">
-        <v>236</v>
+      <c r="B52" s="227" t="s">
+        <v>231</v>
+      </c>
+      <c r="C52" s="169" t="s">
+        <v>232</v>
+      </c>
+      <c r="D52" s="233" t="s">
+        <v>233</v>
       </c>
       <c r="E52" s="112" t="s">
         <v>107</v>
       </c>
-      <c r="F52" s="166" t="s">
-        <v>157</v>
+      <c r="F52" s="164" t="s">
+        <v>154</v>
       </c>
       <c r="G52" s="68" t="s">
         <v>41</v>
@@ -12395,34 +12500,34 @@
       <c r="H52" s="113">
         <v>0</v>
       </c>
-      <c r="I52" s="179" t="s">
-        <v>237</v>
-      </c>
-      <c r="J52" s="246" t="s">
-        <v>236</v>
+      <c r="I52" s="177" t="s">
+        <v>234</v>
+      </c>
+      <c r="J52" s="218" t="s">
+        <v>233</v>
       </c>
       <c r="K52" t="s">
         <v>107</v>
       </c>
       <c r="L52" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A53" s="151">
+      <c r="A53" s="149">
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="B53" s="258"/>
-      <c r="C53" s="145" t="s">
+      <c r="B53" s="234"/>
+      <c r="C53" s="143" t="s">
         <v>110</v>
       </c>
-      <c r="D53" s="258"/>
+      <c r="D53" s="234"/>
       <c r="E53" s="83" t="s">
         <v>112</v>
       </c>
       <c r="F53" s="48" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G53" s="48" t="s">
         <v>41</v>
@@ -12430,36 +12535,36 @@
       <c r="H53" s="116">
         <v>0</v>
       </c>
-      <c r="I53" s="170" t="s">
-        <v>238</v>
-      </c>
-      <c r="J53" s="247"/>
+      <c r="I53" s="168" t="s">
+        <v>235</v>
+      </c>
+      <c r="J53" s="222"/>
       <c r="K53" t="s">
         <v>112</v>
       </c>
       <c r="L53" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A54" s="151">
+      <c r="A54" s="149">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="B54" s="254" t="s">
+      <c r="B54" s="227" t="s">
+        <v>236</v>
+      </c>
+      <c r="C54" s="139" t="s">
+        <v>237</v>
+      </c>
+      <c r="D54" s="233" t="s">
+        <v>238</v>
+      </c>
+      <c r="E54" s="94" t="s">
         <v>239</v>
       </c>
-      <c r="C54" s="141" t="s">
-        <v>240</v>
-      </c>
-      <c r="D54" s="259" t="s">
-        <v>241</v>
-      </c>
-      <c r="E54" s="94" t="s">
-        <v>242</v>
-      </c>
       <c r="F54" s="68" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G54" s="68" t="s">
         <v>31</v>
@@ -12467,32 +12572,32 @@
       <c r="H54" s="118" t="s">
         <v>27</v>
       </c>
-      <c r="I54" s="167"/>
-      <c r="J54" s="246" t="s">
-        <v>241</v>
+      <c r="I54" s="165"/>
+      <c r="J54" s="218" t="s">
+        <v>238</v>
       </c>
       <c r="K54" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="L54" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="55" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A55" s="151">
+      <c r="A55" s="149">
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="B55" s="255"/>
+      <c r="B55" s="228"/>
       <c r="C55" s="35" t="s">
-        <v>243</v>
-      </c>
-      <c r="D55" s="255"/>
+        <v>240</v>
+      </c>
+      <c r="D55" s="228"/>
       <c r="E55" s="36" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F55" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G55" s="37" t="s">
         <v>31</v>
@@ -12500,30 +12605,30 @@
       <c r="H55" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I55" s="168"/>
-      <c r="J55" s="249"/>
+      <c r="I55" s="166"/>
+      <c r="J55" s="221"/>
       <c r="K55" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="L55" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="56" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A56" s="151">
+      <c r="A56" s="149">
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="B56" s="255"/>
+      <c r="B56" s="228"/>
       <c r="C56" s="35" t="s">
-        <v>245</v>
-      </c>
-      <c r="D56" s="255"/>
+        <v>242</v>
+      </c>
+      <c r="D56" s="228"/>
       <c r="E56" s="36" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="F56" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G56" s="37" t="s">
         <v>35</v>
@@ -12531,30 +12636,30 @@
       <c r="H56" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I56" s="168"/>
-      <c r="J56" s="249"/>
+      <c r="I56" s="166"/>
+      <c r="J56" s="221"/>
       <c r="K56" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="L56" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="57" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A57" s="151">
+      <c r="A57" s="149">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="B57" s="255"/>
+      <c r="B57" s="228"/>
       <c r="C57" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="D57" s="255"/>
+        <v>244</v>
+      </c>
+      <c r="D57" s="228"/>
       <c r="E57" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="F57" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G57" s="37" t="s">
         <v>35</v>
@@ -12562,61 +12667,61 @@
       <c r="H57" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I57" s="168"/>
-      <c r="J57" s="249"/>
+      <c r="I57" s="166"/>
+      <c r="J57" s="221"/>
       <c r="K57" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="L57" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="58" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A58" s="151">
+      <c r="A58" s="149">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="B58" s="255"/>
+      <c r="B58" s="228"/>
       <c r="C58" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="D58" s="255"/>
+        <v>246</v>
+      </c>
+      <c r="D58" s="228"/>
       <c r="E58" s="36" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F58" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G58" s="37" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="H58" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I58" s="168"/>
-      <c r="J58" s="249"/>
+      <c r="I58" s="166"/>
+      <c r="J58" s="221"/>
       <c r="K58" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="L58" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="59" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A59" s="151">
+      <c r="A59" s="149">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="B59" s="258"/>
-      <c r="C59" s="169" t="s">
-        <v>251</v>
-      </c>
-      <c r="D59" s="258"/>
+      <c r="B59" s="234"/>
+      <c r="C59" s="167" t="s">
+        <v>248</v>
+      </c>
+      <c r="D59" s="234"/>
       <c r="E59" s="115" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="F59" s="84" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G59" s="48" t="s">
         <v>14</v>
@@ -12624,34 +12729,34 @@
       <c r="H59" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="I59" s="173"/>
-      <c r="J59" s="247"/>
+      <c r="I59" s="171"/>
+      <c r="J59" s="222"/>
       <c r="K59" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="L59" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="60" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A60" s="151">
+      <c r="A60" s="149">
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="B60" s="260" t="s">
-        <v>253</v>
-      </c>
-      <c r="C60" s="171" t="s">
+      <c r="B60" s="235" t="s">
+        <v>250</v>
+      </c>
+      <c r="C60" s="169" t="s">
         <v>85</v>
       </c>
-      <c r="D60" s="261" t="s">
-        <v>254</v>
+      <c r="D60" s="236" t="s">
+        <v>251</v>
       </c>
       <c r="E60" s="112" t="s">
-        <v>255</v>
-      </c>
-      <c r="F60" s="166" t="s">
-        <v>150</v>
+        <v>252</v>
+      </c>
+      <c r="F60" s="164" t="s">
+        <v>147</v>
       </c>
       <c r="G60" s="68" t="s">
         <v>31</v>
@@ -12659,32 +12764,32 @@
       <c r="H60" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="I60" s="179"/>
-      <c r="J60" s="250" t="s">
-        <v>254</v>
+      <c r="I60" s="177"/>
+      <c r="J60" s="223" t="s">
+        <v>251</v>
       </c>
       <c r="K60" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="L60" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="61" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A61" s="151">
+      <c r="A61" s="149">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="B61" s="256"/>
-      <c r="C61" s="169" t="s">
+      <c r="B61" s="229"/>
+      <c r="C61" s="167" t="s">
         <v>89</v>
       </c>
-      <c r="D61" s="258"/>
+      <c r="D61" s="234"/>
       <c r="E61" s="115" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F61" s="84" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G61" s="84" t="s">
         <v>35</v>
@@ -12692,67 +12797,67 @@
       <c r="H61" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="I61" s="173"/>
-      <c r="J61" s="247"/>
+      <c r="I61" s="171"/>
+      <c r="J61" s="222"/>
       <c r="K61" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="L61" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="62" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A62" s="151">
+      <c r="A62" s="149">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="B62" s="254" t="s">
+      <c r="B62" s="227" t="s">
         <v>93</v>
       </c>
-      <c r="C62" s="171" t="s">
+      <c r="C62" s="169" t="s">
         <v>94</v>
       </c>
-      <c r="D62" s="259" t="s">
-        <v>257</v>
+      <c r="D62" s="233" t="s">
+        <v>254</v>
       </c>
       <c r="E62" s="112" t="s">
-        <v>258</v>
-      </c>
-      <c r="F62" s="166" t="s">
-        <v>150</v>
-      </c>
-      <c r="G62" s="166" t="s">
+        <v>255</v>
+      </c>
+      <c r="F62" s="164" t="s">
+        <v>147</v>
+      </c>
+      <c r="G62" s="164" t="s">
         <v>100</v>
       </c>
       <c r="H62" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="I62" s="179"/>
-      <c r="J62" s="246" t="s">
-        <v>257</v>
+      <c r="I62" s="177"/>
+      <c r="J62" s="218" t="s">
+        <v>254</v>
       </c>
       <c r="K62" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="L62" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="63" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A63" s="151">
+      <c r="A63" s="149">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="B63" s="256"/>
-      <c r="C63" s="169" t="s">
-        <v>259</v>
-      </c>
-      <c r="D63" s="258"/>
+      <c r="B63" s="229"/>
+      <c r="C63" s="167" t="s">
+        <v>256</v>
+      </c>
+      <c r="D63" s="234"/>
       <c r="E63" s="115" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="F63" s="84" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G63" s="84" t="s">
         <v>35</v>
@@ -12760,98 +12865,98 @@
       <c r="H63" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="I63" s="173"/>
-      <c r="J63" s="247"/>
+      <c r="I63" s="171"/>
+      <c r="J63" s="222"/>
       <c r="K63" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="L63" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="64" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A64" s="151">
+      <c r="A64" s="149">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="B64" s="254" t="s">
+      <c r="B64" s="227" t="s">
+        <v>258</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D64" s="230" t="s">
+        <v>260</v>
+      </c>
+      <c r="E64" s="112" t="s">
         <v>261</v>
       </c>
-      <c r="C64" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="D64" s="257" t="s">
-        <v>263</v>
-      </c>
-      <c r="E64" s="112" t="s">
-        <v>264</v>
-      </c>
-      <c r="F64" s="166" t="s">
-        <v>157</v>
-      </c>
-      <c r="G64" s="166" t="s">
+      <c r="F64" s="164" t="s">
+        <v>154</v>
+      </c>
+      <c r="G64" s="164" t="s">
         <v>41</v>
       </c>
       <c r="H64" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="I64" s="179"/>
-      <c r="J64" s="251" t="s">
-        <v>263</v>
+      <c r="I64" s="177"/>
+      <c r="J64" s="224" t="s">
+        <v>260</v>
       </c>
       <c r="K64" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="L64" t="s">
-        <v>356</v>
+        <v>321</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A65" s="151">
+      <c r="A65" s="149">
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="B65" s="255"/>
+      <c r="B65" s="228"/>
       <c r="C65" s="24" t="s">
-        <v>265</v>
-      </c>
-      <c r="D65" s="220"/>
+        <v>262</v>
+      </c>
+      <c r="D65" s="231"/>
       <c r="E65" s="36" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="F65" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H65" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I65" s="168"/>
-      <c r="J65" s="252"/>
+      <c r="I65" s="166"/>
+      <c r="J65" s="225"/>
       <c r="K65" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="L65" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="66" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A66" s="151">
+      <c r="A66" s="149">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="B66" s="255"/>
+      <c r="B66" s="228"/>
       <c r="C66" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="D66" s="220"/>
+        <v>265</v>
+      </c>
+      <c r="D66" s="231"/>
       <c r="E66" s="36" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="F66" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G66" s="37" t="s">
         <v>31</v>
@@ -12859,30 +12964,30 @@
       <c r="H66" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="I66" s="168"/>
-      <c r="J66" s="252"/>
+      <c r="I66" s="166"/>
+      <c r="J66" s="225"/>
       <c r="K66" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="L66" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="67" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A67" s="151">
+      <c r="A67" s="149">
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="B67" s="256"/>
-      <c r="C67" s="181" t="s">
-        <v>270</v>
-      </c>
-      <c r="D67" s="221"/>
+      <c r="B67" s="229"/>
+      <c r="C67" s="179" t="s">
+        <v>267</v>
+      </c>
+      <c r="D67" s="232"/>
       <c r="E67" s="115" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="F67" s="48" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G67" s="48" t="s">
         <v>35</v>
@@ -12890,34 +12995,34 @@
       <c r="H67" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="I67" s="173"/>
-      <c r="J67" s="253"/>
+      <c r="I67" s="171"/>
+      <c r="J67" s="226"/>
       <c r="K67" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="L67" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="68" spans="1:12" ht="16.5" thickBot="1">
-      <c r="A68" s="151">
+      <c r="A68" s="149">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="B68" s="254" t="s">
-        <v>272</v>
-      </c>
-      <c r="C68" s="171" t="s">
+      <c r="B68" s="227" t="s">
+        <v>269</v>
+      </c>
+      <c r="C68" s="169" t="s">
         <v>114</v>
       </c>
-      <c r="D68" s="259" t="s">
-        <v>273</v>
+      <c r="D68" s="233" t="s">
+        <v>270</v>
       </c>
       <c r="E68" s="112" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F68" s="68" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G68" s="68" t="s">
         <v>31</v>
@@ -12925,32 +13030,32 @@
       <c r="H68" s="113" t="s">
         <v>27</v>
       </c>
-      <c r="I68" s="179"/>
-      <c r="J68" s="246" t="s">
-        <v>273</v>
+      <c r="I68" s="177"/>
+      <c r="J68" s="218" t="s">
+        <v>270</v>
       </c>
       <c r="K68" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="L68" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="69" spans="1:12" ht="27.75" thickBot="1">
-      <c r="A69" s="151">
+      <c r="A69" s="149">
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="B69" s="258"/>
-      <c r="C69" s="169" t="s">
-        <v>275</v>
-      </c>
-      <c r="D69" s="258"/>
+      <c r="B69" s="234"/>
+      <c r="C69" s="167" t="s">
+        <v>272</v>
+      </c>
+      <c r="D69" s="234"/>
       <c r="E69" s="115" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F69" s="84" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G69" s="84" t="s">
         <v>14</v>
@@ -12958,153 +13063,156 @@
       <c r="H69" s="119" t="s">
         <v>27</v>
       </c>
-      <c r="I69" s="173"/>
-      <c r="J69" s="247"/>
+      <c r="I69" s="171"/>
+      <c r="J69" s="219"/>
       <c r="K69" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="L69" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="70" spans="1:12" ht="41.25" thickBot="1">
-      <c r="A70" s="151">
+      <c r="A70" s="149">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="B70" s="182" t="s">
+      <c r="B70" s="180" t="s">
+        <v>274</v>
+      </c>
+      <c r="C70" s="127" t="s">
+        <v>275</v>
+      </c>
+      <c r="D70" s="181" t="s">
+        <v>276</v>
+      </c>
+      <c r="E70" s="182" t="s">
         <v>277</v>
       </c>
-      <c r="C70" s="127" t="s">
-        <v>278</v>
-      </c>
-      <c r="D70" s="183" t="s">
-        <v>279</v>
-      </c>
-      <c r="E70" s="184" t="s">
-        <v>280</v>
-      </c>
       <c r="F70" s="43" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G70" s="124" t="s">
         <v>31</v>
       </c>
-      <c r="H70" s="177" t="s">
+      <c r="H70" s="175" t="s">
         <v>27</v>
       </c>
-      <c r="I70" s="185"/>
-      <c r="J70" s="206" t="s">
-        <v>279</v>
+      <c r="I70" s="212"/>
+      <c r="J70" s="213" t="s">
+        <v>276</v>
       </c>
       <c r="K70" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="L70" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="71" spans="1:12" ht="16.5" thickBot="1">
-      <c r="B71" s="186"/>
-      <c r="C71" s="186"/>
-      <c r="D71" s="186"/>
-      <c r="E71" s="186"/>
-      <c r="F71" s="186"/>
-      <c r="H71" s="186"/>
+      <c r="B71" s="183"/>
+      <c r="C71" s="183"/>
+      <c r="D71" s="183"/>
+      <c r="E71" s="183"/>
+      <c r="F71" s="183"/>
+      <c r="H71" s="183"/>
     </row>
     <row r="72" spans="1:12" ht="15.75" customHeight="1" thickBot="1">
-      <c r="B72" s="214" t="s">
-        <v>362</v>
-      </c>
-      <c r="C72" s="215"/>
-      <c r="D72" s="215"/>
-      <c r="E72" s="215"/>
-      <c r="F72" s="215"/>
-      <c r="G72" s="215"/>
-      <c r="H72" s="215"/>
-      <c r="I72" s="216"/>
+      <c r="B72" s="215" t="s">
+        <v>327</v>
+      </c>
+      <c r="C72" s="216"/>
+      <c r="D72" s="216"/>
+      <c r="E72" s="216"/>
+      <c r="F72" s="216"/>
+      <c r="G72" s="216"/>
+      <c r="H72" s="216"/>
+      <c r="I72" s="217"/>
     </row>
     <row r="73" spans="1:12" ht="15" customHeight="1" thickBot="1">
-      <c r="B73" s="208"/>
-      <c r="C73" s="209" t="s">
-        <v>363</v>
-      </c>
-      <c r="D73" s="210"/>
-      <c r="E73" s="209" t="s">
-        <v>360</v>
-      </c>
-      <c r="F73" s="210"/>
-      <c r="G73" s="210"/>
-      <c r="H73" s="209" t="s">
-        <v>361</v>
-      </c>
-      <c r="I73" s="209" t="s">
-        <v>358</v>
+      <c r="B73" s="204"/>
+      <c r="C73" s="205" t="s">
+        <v>328</v>
+      </c>
+      <c r="D73" s="206"/>
+      <c r="E73" s="205" t="s">
+        <v>325</v>
+      </c>
+      <c r="F73" s="206"/>
+      <c r="G73" s="206"/>
+      <c r="H73" s="205" t="s">
+        <v>326</v>
+      </c>
+      <c r="I73" s="205" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="74" spans="1:12" ht="15" customHeight="1" thickBot="1">
-      <c r="B74" s="211"/>
-      <c r="C74" s="212" t="s">
-        <v>364</v>
-      </c>
-      <c r="D74" s="213"/>
-      <c r="E74" s="212" t="s">
-        <v>366</v>
-      </c>
-      <c r="F74" s="213"/>
-      <c r="G74" s="213"/>
-      <c r="H74" s="212" t="s">
-        <v>365</v>
-      </c>
-      <c r="I74" s="212" t="s">
-        <v>369</v>
+      <c r="B74" s="207"/>
+      <c r="C74" s="208" t="s">
+        <v>329</v>
+      </c>
+      <c r="D74" s="209"/>
+      <c r="E74" s="208" t="s">
+        <v>331</v>
+      </c>
+      <c r="F74" s="209"/>
+      <c r="G74" s="209"/>
+      <c r="H74" s="208" t="s">
+        <v>330</v>
+      </c>
+      <c r="I74" s="208" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:12" ht="15" customHeight="1" thickBot="1">
-      <c r="B75" s="211"/>
-      <c r="C75" s="213"/>
-      <c r="D75" s="213"/>
-      <c r="E75" s="212" t="s">
-        <v>367</v>
-      </c>
-      <c r="F75" s="213"/>
-      <c r="G75" s="213"/>
-      <c r="H75" s="212" t="s">
+      <c r="B75" s="207"/>
+      <c r="C75" s="208" t="s">
+        <v>329</v>
+      </c>
+      <c r="D75" s="209"/>
+      <c r="E75" s="208" t="s">
+        <v>332</v>
+      </c>
+      <c r="F75" s="209"/>
+      <c r="G75" s="209"/>
+      <c r="H75" s="208" t="s">
         <v>52</v>
       </c>
-      <c r="I75" s="213"/>
+      <c r="I75" s="214" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="76" spans="1:12" ht="15" customHeight="1" thickBot="1">
-      <c r="B76" s="211"/>
-      <c r="C76" s="213"/>
-      <c r="D76" s="213"/>
-      <c r="E76" s="212"/>
-      <c r="F76" s="213"/>
-      <c r="G76" s="213"/>
-      <c r="H76" s="212"/>
-      <c r="I76" s="212"/>
+      <c r="B76" s="207"/>
+      <c r="C76" s="209"/>
+      <c r="D76" s="209"/>
+      <c r="E76" s="208"/>
+      <c r="F76" s="209"/>
+      <c r="G76" s="209"/>
+      <c r="H76" s="208"/>
+      <c r="I76" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="B62:B63"/>
-    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="J1:L1"/>
     <mergeCell ref="B1:C1"/>
     <mergeCell ref="D1:H1"/>
-    <mergeCell ref="B5:B20"/>
     <mergeCell ref="D5:D20"/>
     <mergeCell ref="B21:B34"/>
     <mergeCell ref="D21:D34"/>
-    <mergeCell ref="B54:B59"/>
-    <mergeCell ref="B60:B61"/>
     <mergeCell ref="D35:D40"/>
     <mergeCell ref="D54:D59"/>
     <mergeCell ref="D60:D61"/>
     <mergeCell ref="B35:B40"/>
     <mergeCell ref="B42:B51"/>
     <mergeCell ref="D42:D51"/>
+    <mergeCell ref="B68:B69"/>
+    <mergeCell ref="D68:D69"/>
     <mergeCell ref="B52:B53"/>
     <mergeCell ref="D52:D53"/>
-    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="B54:B59"/>
+    <mergeCell ref="B60:B61"/>
     <mergeCell ref="B72:I72"/>
     <mergeCell ref="J68:J69"/>
     <mergeCell ref="J5:J20"/>
@@ -13118,8 +13226,9 @@
     <mergeCell ref="J64:J67"/>
     <mergeCell ref="B64:B67"/>
     <mergeCell ref="D64:D67"/>
-    <mergeCell ref="B68:B69"/>
-    <mergeCell ref="D68:D69"/>
+    <mergeCell ref="B62:B63"/>
+    <mergeCell ref="D62:D63"/>
+    <mergeCell ref="B5:B20"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -13139,252 +13248,252 @@
     <col min="5" max="5" width="13.875" customWidth="1"/>
     <col min="6" max="6" width="8.25" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.625" customWidth="1"/>
+    <col min="8" max="8" width="15.5" customWidth="1"/>
     <col min="9" max="9" width="19.375" customWidth="1"/>
     <col min="10" max="26" width="6.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15.75">
-      <c r="A1" s="149"/>
-      <c r="B1" s="262" t="s">
+      <c r="A1" s="147"/>
+      <c r="B1" s="239" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="269"/>
-      <c r="D1" s="264" t="s">
+      <c r="C1" s="271"/>
+      <c r="D1" s="241" t="s">
+        <v>140</v>
+      </c>
+      <c r="E1" s="242"/>
+      <c r="F1" s="242"/>
+      <c r="G1" s="242"/>
+      <c r="H1" s="271"/>
+      <c r="I1" s="184" t="s">
+        <v>141</v>
+      </c>
+      <c r="J1" s="185"/>
+    </row>
+    <row r="2" spans="1:10" ht="27">
+      <c r="A2" s="149" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="150" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="151" t="s">
+        <v>142</v>
+      </c>
+      <c r="D2" s="152" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="265"/>
-      <c r="F1" s="265"/>
-      <c r="G1" s="265"/>
-      <c r="H1" s="269"/>
-      <c r="I1" s="187" t="s">
+      <c r="E2" s="153" t="s">
         <v>144</v>
       </c>
-      <c r="J1" s="188"/>
-    </row>
-    <row r="2" spans="1:10" ht="27">
-      <c r="A2" s="151" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="152" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="153" t="s">
+      <c r="F2" s="153" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="153" t="s">
         <v>145</v>
       </c>
-      <c r="D2" s="154" t="s">
-        <v>146</v>
-      </c>
-      <c r="E2" s="155" t="s">
-        <v>147</v>
-      </c>
-      <c r="F2" s="155" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="155" t="s">
-        <v>148</v>
-      </c>
-      <c r="H2" s="156" t="s">
+      <c r="H2" s="154" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="189"/>
+      <c r="I2" s="186"/>
     </row>
     <row r="3" spans="1:10" ht="54">
-      <c r="A3" s="151">
+      <c r="A3" s="149">
         <f t="shared" ref="A3:A10" si="0">ROW()-2</f>
         <v>1</v>
       </c>
-      <c r="B3" s="158" t="s">
-        <v>281</v>
+      <c r="B3" s="156" t="s">
+        <v>278</v>
       </c>
       <c r="C3" s="54" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D3" s="91" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="E3" s="92"/>
-      <c r="F3" s="161" t="s">
-        <v>157</v>
+      <c r="F3" s="159" t="s">
+        <v>154</v>
       </c>
       <c r="G3" s="73" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="190"/>
-      <c r="I3" s="191"/>
+      <c r="H3" s="187"/>
+      <c r="I3" s="188"/>
     </row>
     <row r="4" spans="1:10" ht="15.75">
-      <c r="A4" s="151">
+      <c r="A4" s="149">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="B4" s="260" t="s">
+      <c r="B4" s="235" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" s="189" t="s">
+        <v>282</v>
+      </c>
+      <c r="D4" s="269" t="s">
+        <v>283</v>
+      </c>
+      <c r="E4" s="94" t="s">
         <v>284</v>
       </c>
-      <c r="C4" s="192" t="s">
+      <c r="F4" s="164" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" s="68" t="s">
         <v>285</v>
       </c>
-      <c r="D4" s="267" t="s">
-        <v>286</v>
-      </c>
-      <c r="E4" s="94" t="s">
-        <v>287</v>
-      </c>
-      <c r="F4" s="166" t="s">
-        <v>150</v>
-      </c>
-      <c r="G4" s="68" t="s">
-        <v>288</v>
-      </c>
-      <c r="H4" s="193"/>
-      <c r="I4" s="194" t="s">
-        <v>233</v>
+      <c r="H4" s="190"/>
+      <c r="I4" s="191" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="15.75">
-      <c r="A5" s="151">
+      <c r="A5" s="149">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="255"/>
-      <c r="C5" s="195" t="s">
-        <v>289</v>
-      </c>
-      <c r="D5" s="255"/>
+      <c r="B5" s="228"/>
+      <c r="C5" s="192" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" s="228"/>
       <c r="E5" s="36" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F5" s="37" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="H5" s="196"/>
-      <c r="I5" s="197" t="s">
-        <v>233</v>
+        <v>285</v>
+      </c>
+      <c r="H5" s="193"/>
+      <c r="I5" s="194" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="27">
-      <c r="A6" s="151">
+      <c r="A6" s="149">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="270"/>
-      <c r="C6" s="198"/>
-      <c r="D6" s="258"/>
+      <c r="B6" s="272"/>
+      <c r="C6" s="195"/>
+      <c r="D6" s="234"/>
       <c r="E6" s="83" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F6" s="84" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G6" s="84" t="s">
         <v>41</v>
       </c>
-      <c r="H6" s="199" t="s">
-        <v>292</v>
-      </c>
-      <c r="I6" s="200" t="s">
-        <v>233</v>
+      <c r="H6" s="196" t="s">
+        <v>289</v>
+      </c>
+      <c r="I6" s="197" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="15.75">
-      <c r="A7" s="151">
+      <c r="A7" s="149">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="254" t="s">
+      <c r="B7" s="227" t="s">
+        <v>290</v>
+      </c>
+      <c r="C7" s="189" t="s">
+        <v>291</v>
+      </c>
+      <c r="D7" s="269" t="s">
+        <v>292</v>
+      </c>
+      <c r="E7" s="94" t="s">
         <v>293</v>
       </c>
-      <c r="C7" s="192" t="s">
-        <v>294</v>
-      </c>
-      <c r="D7" s="267" t="s">
-        <v>295</v>
-      </c>
-      <c r="E7" s="94" t="s">
-        <v>296</v>
-      </c>
-      <c r="F7" s="166" t="s">
-        <v>157</v>
+      <c r="F7" s="164" t="s">
+        <v>154</v>
       </c>
       <c r="G7" s="118" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="193" t="s">
-        <v>292</v>
-      </c>
-      <c r="I7" s="194" t="s">
-        <v>233</v>
+      <c r="H7" s="190" t="s">
+        <v>289</v>
+      </c>
+      <c r="I7" s="191" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="15.75">
-      <c r="A8" s="151">
+      <c r="A8" s="149">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="270"/>
-      <c r="C8" s="195" t="s">
-        <v>297</v>
-      </c>
-      <c r="D8" s="258"/>
+      <c r="B8" s="272"/>
+      <c r="C8" s="192" t="s">
+        <v>294</v>
+      </c>
+      <c r="D8" s="234"/>
       <c r="E8" s="36" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F8" s="37" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="G8" s="116" t="s">
         <v>41</v>
       </c>
-      <c r="H8" s="199" t="s">
-        <v>292</v>
-      </c>
-      <c r="I8" s="200" t="s">
-        <v>233</v>
+      <c r="H8" s="196" t="s">
+        <v>289</v>
+      </c>
+      <c r="I8" s="197" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="15.75">
-      <c r="A9" s="151">
+      <c r="A9" s="149">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="254" t="s">
+      <c r="B9" s="227" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" s="198" t="s">
+        <v>297</v>
+      </c>
+      <c r="D9" s="269" t="s">
+        <v>298</v>
+      </c>
+      <c r="E9" s="112" t="s">
         <v>299</v>
       </c>
-      <c r="C9" s="201" t="s">
+      <c r="F9" s="68" t="s">
+        <v>147</v>
+      </c>
+      <c r="G9" s="164" t="s">
         <v>300</v>
       </c>
-      <c r="D9" s="267" t="s">
+      <c r="H9" s="190"/>
+      <c r="I9" s="270" t="s">
         <v>301</v>
       </c>
-      <c r="E9" s="112" t="s">
-        <v>302</v>
-      </c>
-      <c r="F9" s="68" t="s">
-        <v>150</v>
-      </c>
-      <c r="G9" s="166" t="s">
-        <v>303</v>
-      </c>
-      <c r="H9" s="193"/>
-      <c r="I9" s="268" t="s">
-        <v>304</v>
-      </c>
     </row>
     <row r="10" spans="1:10" ht="27">
-      <c r="A10" s="151">
+      <c r="A10" s="149">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="270"/>
-      <c r="C10" s="198" t="s">
-        <v>305</v>
-      </c>
-      <c r="D10" s="258"/>
+      <c r="B10" s="272"/>
+      <c r="C10" s="195" t="s">
+        <v>302</v>
+      </c>
+      <c r="D10" s="234"/>
       <c r="E10" s="36" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F10" s="37" t="s">
         <v>35</v>
@@ -13392,90 +13501,90 @@
       <c r="G10" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="199"/>
-      <c r="I10" s="258"/>
+      <c r="H10" s="196"/>
+      <c r="I10" s="234"/>
     </row>
     <row r="11" spans="1:10" ht="15.75">
-      <c r="B11" s="186"/>
-      <c r="C11" s="186"/>
-      <c r="D11" s="186"/>
-      <c r="E11" s="186"/>
-      <c r="F11" s="186"/>
-      <c r="G11" s="186"/>
-      <c r="H11" s="186"/>
-      <c r="I11" s="186"/>
+      <c r="B11" s="183"/>
+      <c r="C11" s="183"/>
+      <c r="D11" s="183"/>
+      <c r="E11" s="183"/>
+      <c r="F11" s="183"/>
+      <c r="G11" s="183"/>
+      <c r="H11" s="183"/>
+      <c r="I11" s="183"/>
     </row>
     <row r="12" spans="1:10" ht="15.75"/>
     <row r="13" spans="1:10" ht="15.75"/>
     <row r="14" spans="1:10" ht="15.75"/>
     <row r="15" spans="1:10" ht="16.5" thickBot="1"/>
     <row r="16" spans="1:10" ht="16.5" thickBot="1">
-      <c r="B16" s="214" t="s">
-        <v>362</v>
-      </c>
-      <c r="C16" s="215"/>
-      <c r="D16" s="215"/>
-      <c r="E16" s="215"/>
-      <c r="F16" s="215"/>
-      <c r="G16" s="215"/>
-      <c r="H16" s="215"/>
-      <c r="I16" s="216"/>
-    </row>
-    <row r="17" spans="2:9" ht="32.25" thickBot="1">
-      <c r="B17" s="208"/>
-      <c r="C17" s="209" t="s">
-        <v>363</v>
-      </c>
-      <c r="D17" s="210"/>
-      <c r="E17" s="209" t="s">
-        <v>360</v>
-      </c>
-      <c r="F17" s="210"/>
-      <c r="G17" s="210"/>
-      <c r="H17" s="209" t="s">
-        <v>361</v>
-      </c>
-      <c r="I17" s="209" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9" ht="45.75" thickBot="1">
-      <c r="B18" s="211"/>
-      <c r="C18" s="212" t="s">
-        <v>364</v>
-      </c>
-      <c r="D18" s="213"/>
-      <c r="E18" s="212" t="s">
-        <v>366</v>
-      </c>
-      <c r="F18" s="213"/>
-      <c r="G18" s="213"/>
-      <c r="H18" s="212" t="s">
-        <v>368</v>
-      </c>
-      <c r="I18" s="212" t="s">
-        <v>369</v>
+      <c r="B16" s="215" t="s">
+        <v>327</v>
+      </c>
+      <c r="C16" s="216"/>
+      <c r="D16" s="216"/>
+      <c r="E16" s="216"/>
+      <c r="F16" s="216"/>
+      <c r="G16" s="216"/>
+      <c r="H16" s="216"/>
+      <c r="I16" s="217"/>
+    </row>
+    <row r="17" spans="2:9" ht="16.5" thickBot="1">
+      <c r="B17" s="204"/>
+      <c r="C17" s="205" t="s">
+        <v>328</v>
+      </c>
+      <c r="D17" s="206"/>
+      <c r="E17" s="205" t="s">
+        <v>325</v>
+      </c>
+      <c r="F17" s="206"/>
+      <c r="G17" s="206"/>
+      <c r="H17" s="205" t="s">
+        <v>326</v>
+      </c>
+      <c r="I17" s="205" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="30.75" thickBot="1">
+      <c r="B18" s="207"/>
+      <c r="C18" s="208" t="s">
+        <v>329</v>
+      </c>
+      <c r="D18" s="209"/>
+      <c r="E18" s="208" t="s">
+        <v>331</v>
+      </c>
+      <c r="F18" s="209"/>
+      <c r="G18" s="209"/>
+      <c r="H18" s="208" t="s">
+        <v>280</v>
+      </c>
+      <c r="I18" s="208" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="19" spans="2:9" ht="16.5" thickBot="1">
-      <c r="B19" s="211"/>
-      <c r="C19" s="213"/>
-      <c r="D19" s="213"/>
-      <c r="E19" s="212"/>
-      <c r="F19" s="213"/>
-      <c r="G19" s="213"/>
-      <c r="H19" s="212"/>
-      <c r="I19" s="213"/>
+      <c r="B19" s="207"/>
+      <c r="C19" s="209"/>
+      <c r="D19" s="209"/>
+      <c r="E19" s="208"/>
+      <c r="F19" s="209"/>
+      <c r="G19" s="209"/>
+      <c r="H19" s="208"/>
+      <c r="I19" s="209"/>
     </row>
     <row r="20" spans="2:9" ht="16.5" thickBot="1">
-      <c r="B20" s="211"/>
-      <c r="C20" s="213"/>
-      <c r="D20" s="213"/>
-      <c r="E20" s="212"/>
-      <c r="F20" s="213"/>
-      <c r="G20" s="213"/>
-      <c r="H20" s="212"/>
-      <c r="I20" s="212"/>
+      <c r="B20" s="207"/>
+      <c r="C20" s="209"/>
+      <c r="D20" s="209"/>
+      <c r="E20" s="208"/>
+      <c r="F20" s="209"/>
+      <c r="G20" s="209"/>
+      <c r="H20" s="208"/>
+      <c r="I20" s="208"/>
     </row>
   </sheetData>
   <mergeCells count="10">
